--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_La Laguna Tenerife.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_La Laguna Tenerife.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>235.84</v>
+        <v>376.6</v>
       </c>
       <c r="C2" t="n">
-        <v>234.94</v>
+        <v>375.08</v>
       </c>
       <c r="D2" t="n">
-        <v>122.5844896569337</v>
+        <v>118.3747467206996</v>
       </c>
       <c r="E2" t="n">
-        <v>131.9485826168383</v>
+        <v>135.1711634851232</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6102564102564103</v>
+        <v>0.5696594427244582</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1156115452081008</v>
+        <v>0.1211827435773146</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.2130177514792899</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="J2" t="n">
+        <v>37</v>
+      </c>
+      <c r="K2" t="n">
+        <v>41</v>
+      </c>
+      <c r="L2" t="n">
         <v>27</v>
       </c>
-      <c r="K2" t="n">
-        <v>21</v>
-      </c>
-      <c r="L2" t="n">
-        <v>19</v>
-      </c>
       <c r="M2" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="N2" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="O2" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="Q2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1282051282051282</v>
+        <v>0.130030959752322</v>
       </c>
       <c r="T2" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="U2" t="n">
+        <v>68</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="W2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X2" t="n">
         <v>31</v>
       </c>
-      <c r="V2" t="n">
-        <v>0.158974358974359</v>
-      </c>
-      <c r="W2" t="n">
-        <v>10</v>
-      </c>
-      <c r="X2" t="n">
-        <v>20</v>
-      </c>
       <c r="Y2" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.09597523219814241</v>
       </c>
       <c r="Z2" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="AA2" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3538461538461539</v>
+        <v>0.3281733746130031</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.72</v>
+        <v>0.7236842105263158</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.32</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.3679245283018868</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.44</v>
+        <v>1.447368421052632</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.967741935483871</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.348314606741573</v>
+        <v>1.226277372262774</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.125</v>
+        <v>0.8809523809523809</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.4</v>
+        <v>1.138888888888889</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.111111111111111</v>
+        <v>1.8</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.758620689655172</v>
+        <v>1.68</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.724137931034483</v>
+        <v>6.46</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.482758620689655</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.61333333333334</v>
+        <v>75.32000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>78.31333333333333</v>
+        <v>75.01599999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>122.5844896569337</v>
+        <v>118.3747467206996</v>
       </c>
       <c r="E3" t="n">
-        <v>131.9485826168383</v>
+        <v>135.1711634851232</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6102564102564103</v>
+        <v>0.5696594427244582</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1156115452081008</v>
+        <v>0.1211827435773146</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.2130177514792899</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>6.333333333333333</v>
+        <v>5.4</v>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>16.66666666666667</v>
+        <v>15.2</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.666666666666667</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>8.333333333333334</v>
+        <v>8.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1282051282051282</v>
+        <v>0.130030959752322</v>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="U3" t="n">
-        <v>10.33333333333333</v>
+        <v>13.6</v>
       </c>
       <c r="V3" t="n">
-        <v>0.158974358974359</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="W3" t="n">
-        <v>3.333333333333333</v>
+        <v>3.4</v>
       </c>
       <c r="X3" t="n">
-        <v>6.666666666666667</v>
+        <v>6.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.09597523219814243</v>
       </c>
       <c r="Z3" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>23</v>
+        <v>21.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3538461538461539</v>
+        <v>0.3281733746130031</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.72</v>
+        <v>0.7236842105263158</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.32</v>
+        <v>0.4047619047619047</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4838709677419354</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.3679245283018868</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.44</v>
+        <v>1.447368421052632</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.9677419354838709</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.348314606741573</v>
+        <v>1.226277372262774</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.125</v>
+        <v>0.8809523809523809</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.4</v>
+        <v>1.138888888888889</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.111111111111111</v>
+        <v>1.8</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.758620689655173</v>
+        <v>1.68</v>
       </c>
       <c r="AO3" t="n">
-        <v>6.724137931034483</v>
+        <v>6.459999999999999</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.482758620689655</v>
+        <v>8.139999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>234.04</v>
+        <v>373.5599999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>234.94</v>
+        <v>375.08</v>
       </c>
       <c r="D4" t="n">
-        <v>131.9485826168383</v>
+        <v>135.1711634851232</v>
       </c>
       <c r="E4" t="n">
-        <v>122.5844896569337</v>
+        <v>118.3747467206996</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5989847715736041</v>
+        <v>0.6151515151515151</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09193993257738278</v>
+        <v>0.09846211552888222</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2967032967032967</v>
+        <v>0.3486842105263158</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3756345177664975</v>
+        <v>0.306060606060606</v>
       </c>
       <c r="J4" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="L4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M4" t="n">
+        <v>37</v>
+      </c>
+      <c r="N4" t="n">
+        <v>86</v>
+      </c>
+      <c r="O4" t="n">
+        <v>109</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.3303030303030303</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>32</v>
+      </c>
+      <c r="R4" t="n">
+        <v>61</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1848484848484848</v>
+      </c>
+      <c r="T4" t="n">
+        <v>22</v>
+      </c>
+      <c r="U4" t="n">
+        <v>48</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1454545454545454</v>
+      </c>
+      <c r="W4" t="n">
+        <v>10</v>
+      </c>
+      <c r="X4" t="n">
         <v>20</v>
       </c>
-      <c r="N4" t="n">
-        <v>69</v>
-      </c>
-      <c r="O4" t="n">
-        <v>86</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.4365482233502538</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>13</v>
-      </c>
-      <c r="R4" t="n">
-        <v>31</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.1573604060913706</v>
-      </c>
-      <c r="T4" t="n">
-        <v>6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>18</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.09137055837563451</v>
-      </c>
-      <c r="W4" t="n">
-        <v>6</v>
-      </c>
-      <c r="X4" t="n">
-        <v>14</v>
-      </c>
       <c r="Y4" t="n">
-        <v>0.07106598984771574</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="AA4" t="n">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2436548223350254</v>
+        <v>0.2787878787878788</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8023255813953488</v>
+        <v>0.7889908256880734</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.5245901639344263</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.604651162790698</v>
+        <v>1.577981651376147</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.967741935483871</v>
+        <v>1.125</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.074074074074074</v>
+        <v>1.056603773584906</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.470588235294118</v>
+        <v>1.6</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.166666666666667</v>
+        <v>2.023809523809524</v>
       </c>
       <c r="AO4" t="n">
-        <v>8.208333333333334</v>
+        <v>7.857142857142857</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.375</v>
+        <v>9.880952380952381</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.01333333333332</v>
+        <v>74.71199999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>78.31333333333333</v>
+        <v>75.01599999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>131.9485826168383</v>
+        <v>135.1711634851232</v>
       </c>
       <c r="E5" t="n">
-        <v>122.5844896569337</v>
+        <v>118.3747467206996</v>
       </c>
       <c r="F5" t="n">
-        <v>0.598984771573604</v>
+        <v>0.6151515151515152</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09193993257738277</v>
+        <v>0.0984621155288822</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2967032967032967</v>
+        <v>0.3486842105263158</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3756345177664975</v>
+        <v>0.306060606060606</v>
       </c>
       <c r="J5" t="n">
-        <v>9.666666666666666</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>9.666666666666666</v>
+        <v>11.2</v>
       </c>
       <c r="L5" t="n">
-        <v>8.333333333333334</v>
+        <v>6.4</v>
       </c>
       <c r="M5" t="n">
-        <v>6.666666666666667</v>
+        <v>7.4</v>
       </c>
       <c r="N5" t="n">
-        <v>23</v>
+        <v>17.2</v>
       </c>
       <c r="O5" t="n">
-        <v>28.66666666666667</v>
+        <v>21.8</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4365482233502538</v>
+        <v>0.3303030303030303</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.333333333333333</v>
+        <v>6.4</v>
       </c>
       <c r="R5" t="n">
-        <v>10.33333333333333</v>
+        <v>12.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1573604060913706</v>
+        <v>0.1848484848484848</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="U5" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09137055837563451</v>
+        <v>0.1454545454545454</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>4.666666666666667</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.07106598984771574</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.666666666666667</v>
+        <v>6.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>16</v>
+        <v>18.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2436548223350254</v>
+        <v>0.2787878787878788</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8023255813953488</v>
+        <v>0.7889908256880733</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.5245901639344263</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4583333333333334</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3478260869565218</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.604651162790698</v>
+        <v>1.577981651376147</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9677419354838709</v>
+        <v>1.125</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.074074074074074</v>
+        <v>1.056603773584906</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.470588235294118</v>
+        <v>1.6</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.166666666666667</v>
+        <v>2.023809523809524</v>
       </c>
       <c r="AO5" t="n">
-        <v>8.208333333333334</v>
+        <v>7.857142857142857</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.375</v>
+        <v>9.880952380952381</v>
       </c>
     </row>
     <row r="7">
@@ -1419,67 +1419,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19</v>
+      </c>
+      <c r="H8" t="n">
         <v>11</v>
       </c>
-      <c r="F8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" t="n">
-        <v>12</v>
-      </c>
-      <c r="H8" t="n">
-        <v>9</v>
-      </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J8" t="n">
+        <v>16</v>
+      </c>
+      <c r="K8" t="n">
         <v>10</v>
       </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T8" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1509,66 +1509,66 @@
         <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG8" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ8" t="n">
+      <c r="AK8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>94:36</t>
+        </is>
+      </c>
+      <c r="AO8" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AT8" t="n">
         <v>0.333</v>
       </c>
-      <c r="AK8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>61:27</t>
-        </is>
-      </c>
-      <c r="AO8" t="n">
-        <v>33.28</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.172</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0.391</v>
-      </c>
       <c r="AU8" t="n">
-        <v>2</v>
+        <v>2.667</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.259</v>
+        <v>0.231</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.107</v>
+        <v>0.139</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.115</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="9">
@@ -1578,37 +1578,37 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>11</v>
+      </c>
+      <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="C9" t="n">
-        <v>28</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="K9" t="n">
         <v>5</v>
       </c>
-      <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1626,108 +1626,108 @@
         <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>6</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI9" t="n">
         <v>4</v>
       </c>
-      <c r="T9" t="n">
-        <v>10</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>2</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AK9" t="n">
         <v>3</v>
       </c>
       <c r="AL9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>39:52</t>
+          <t>72:10</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>25.52</v>
+        <v>35.84</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.618</v>
+        <v>0.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.097</v>
+        <v>0.977</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.196</v>
+        <v>0.14</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.412</v>
+        <v>0.346</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.306</v>
+        <v>0.241</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.03</v>
+        <v>0.033</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.033</v>
+        <v>0.091</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="10">
@@ -1737,67 +1737,67 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>23</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>15</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="U10" t="n">
         <v>8</v>
       </c>
       <c r="V10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
@@ -1809,28 +1809,28 @@
         <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AF10" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.333</v>
+        <v>0.455</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1845,48 +1845,48 @@
         <v>5</v>
       </c>
       <c r="AL10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.417</v>
+        <v>0.357</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>64:05</t>
+          <t>103:12</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>30.76</v>
+        <v>58.52</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.5</v>
+        <v>0.459</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.522</v>
+        <v>0.495</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.975</v>
+        <v>0.889</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.065</v>
+        <v>0.103</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.111</v>
+        <v>0.143</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.5</v>
+        <v>3.833</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.23</v>
+        <v>0.275</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.038</v>
+        <v>0.034</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.062</v>
+        <v>0.064</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="11">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
@@ -1905,13 +1905,13 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1920,13 +1920,13 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1938,19 +1938,19 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
         <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1968,10 +1968,10 @@
         <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1986,10 +1986,10 @@
         <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -2004,45 +2004,45 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>36:42</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.5</v>
+        <v>0.308</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.25</v>
+        <v>0.308</v>
       </c>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.165</v>
+        <v>0.172</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.171</v>
+        <v>0.108</v>
       </c>
       <c r="AY11" t="n">
         <v>0.052</v>
@@ -2055,156 +2055,156 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>36</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="n">
-        <v>15</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="Q12" t="n">
         <v>3</v>
       </c>
-      <c r="E12" t="n">
+      <c r="R12" t="n">
+        <v>10</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>51</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" t="n">
         <v>7</v>
       </c>
-      <c r="F12" t="n">
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
         <v>3</v>
       </c>
-      <c r="G12" t="n">
-        <v>6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="AC12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI12" t="n">
         <v>3</v>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>8</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="AJ12" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AK12" t="n">
         <v>4</v>
       </c>
-      <c r="T12" t="n">
-        <v>25</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>2</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2</v>
-      </c>
       <c r="AL12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>77:10</t>
+          <t>132:58</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.577</v>
+        <v>0.783</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.577</v>
+        <v>0.783</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.071</v>
+        <v>1.385</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.115</v>
       </c>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.095</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.031</v>
+        <v>0.036</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.188</v>
+        <v>0.129</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.054</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="13">
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
@@ -2229,7 +2229,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
@@ -2241,13 +2241,13 @@
         <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -2322,48 +2322,48 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>39:22</t>
+          <t>55:48</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>7.88</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.654</v>
+        <v>0.571</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.142</v>
+        <v>1.014</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.127</v>
+        <v>0.113</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AU13" t="n">
         <v>2</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.096</v>
+        <v>0.077</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.234</v>
+        <v>0.189</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.021</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="14">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.366</v>
+        <v>0.371</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -2532,61 +2532,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H15" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>12</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
         <v>4</v>
       </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2</v>
-      </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
+        <v>15</v>
+      </c>
+      <c r="S15" t="n">
         <v>11</v>
       </c>
-      <c r="S15" t="n">
-        <v>7</v>
-      </c>
       <c r="T15" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="U15" t="n">
         <v>2</v>
@@ -2595,93 +2595,93 @@
         <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC15" t="n">
         <v>6</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AD15" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>0.667</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC15" t="n">
+      <c r="AK15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL15" t="n">
         <v>5</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AM15" t="n">
         <v>0.4</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>60:09</t>
+          <t>103:25</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>19.64</v>
+        <v>34.4</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.588</v>
+        <v>0.483</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.611</v>
+        <v>0.539</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.222</v>
+        <v>1.047</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.235</v>
+        <v>0.276</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.156</v>
+        <v>0.161</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.081</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AX15" t="n">
         <v>0.153</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.022</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="16">
@@ -2691,100 +2691,100 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
         <v>7</v>
       </c>
       <c r="I16" t="n">
+        <v>12</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
         <v>11</v>
       </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>9</v>
-      </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
+        <v>13</v>
+      </c>
+      <c r="S16" t="n">
+        <v>14</v>
+      </c>
+      <c r="T16" t="n">
+        <v>61</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
         <v>7</v>
       </c>
-      <c r="S16" t="n">
-        <v>12</v>
-      </c>
-      <c r="T16" t="n">
-        <v>47</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF16" t="n">
         <v>6</v>
       </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>3</v>
-      </c>
       <c r="AG16" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -2799,48 +2799,48 @@
         <v>3</v>
       </c>
       <c r="AL16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.6</v>
+        <v>0.429</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>60:56</t>
+          <t>87:21</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>34.84</v>
+        <v>53.28</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.625</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.629</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.263</v>
+        <v>1.164</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.259</v>
+        <v>0.159</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.274</v>
+        <v>0.296</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.02</v>
+        <v>0.081</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.195</v>
+        <v>0.166</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="17">
@@ -2850,22 +2850,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2874,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2892,19 +2892,19 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2928,13 +2928,13 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2958,18 +2958,18 @@
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>36:31</t>
+          <t>46:58</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AP17" t="n">
         <v>0.5</v>
@@ -2978,71 +2978,71 @@
         <v>0.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.039</v>
+        <v>0.062</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.108</v>
+        <v>0.112</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>#42 A. DOORNEKAMP</t>
+          <t>#35 F. GUERRA</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>13</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
         <v>3</v>
       </c>
-      <c r="C18" t="n">
-        <v>35</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6</v>
-      </c>
-      <c r="E18" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" t="n">
-        <v>7</v>
-      </c>
-      <c r="G18" t="n">
-        <v>15</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>7</v>
-      </c>
-      <c r="K18" t="n">
-        <v>6</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3051,158 +3051,158 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>22</v>
+      </c>
+      <c r="U18" t="n">
         <v>4</v>
       </c>
-      <c r="T18" t="n">
-        <v>33</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
         <v>3</v>
       </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>6</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1</v>
-      </c>
       <c r="Z18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AB18" t="n">
         <v>1</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>30:53</t>
+        </is>
+      </c>
+      <c r="AO18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AP18" t="n">
         <v>0.667</v>
       </c>
-      <c r="AH18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>81:24</t>
-        </is>
-      </c>
-      <c r="AO18" t="n">
-        <v>25.88</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0.717</v>
-      </c>
       <c r="AQ18" t="n">
-        <v>0.733</v>
+        <v>0.793</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.352</v>
+        <v>1.413</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.077</v>
+        <v>0.109</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.152</v>
+        <v>0.144</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.015</v>
+        <v>0.115</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.097</v>
+        <v>0.17</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.081</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>#88 P. MILLS</t>
+          <t>#42 A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
         <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H19" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
+        <v>8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>12</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
         <v>3</v>
       </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
@@ -3210,40 +3210,40 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>15</v>
+      </c>
+      <c r="S19" t="n">
         <v>6</v>
       </c>
-      <c r="Q19" t="n">
-        <v>6</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
+        <v>42</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2</v>
+      </c>
+      <c r="W19" t="n">
         <v>8</v>
-      </c>
-      <c r="S19" t="n">
-        <v>15</v>
-      </c>
-      <c r="T19" t="n">
-        <v>48</v>
-      </c>
-      <c r="U19" t="n">
-        <v>9</v>
-      </c>
-      <c r="V19" t="n">
-        <v>3</v>
-      </c>
-      <c r="W19" t="n">
-        <v>5</v>
       </c>
       <c r="X19" t="n">
         <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
         <v>2</v>
@@ -3255,384 +3255,384 @@
         <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.429</v>
+        <v>0.667</v>
       </c>
       <c r="AH19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ19" t="n">
         <v>0.333</v>
       </c>
       <c r="AK19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.545</v>
+        <v>0.357</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>53:18</t>
+          <t>125:37</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>43.16</v>
+        <v>34.76</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.661</v>
+        <v>0.629</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.74</v>
+        <v>0.656</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.274</v>
+        <v>1.237</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.139</v>
+        <v>0.058</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.452</v>
+        <v>0.129</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.387</v>
+        <v>0.134</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.025</v>
+        <v>0.126</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.037</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>#88 P. MILLS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.467</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>0.478</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>108:59</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>0.669</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>0.728</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.271</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>0.127</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>0.356</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
         <v>3</v>
       </c>
-      <c r="C21" t="n">
-        <v>288</v>
-      </c>
-      <c r="D21" t="n">
-        <v>59</v>
-      </c>
-      <c r="E21" t="n">
-        <v>106</v>
-      </c>
-      <c r="F21" t="n">
-        <v>40</v>
-      </c>
-      <c r="G21" t="n">
-        <v>89</v>
-      </c>
-      <c r="H21" t="n">
-        <v>50</v>
-      </c>
-      <c r="I21" t="n">
-        <v>61</v>
-      </c>
-      <c r="J21" t="n">
-        <v>51</v>
-      </c>
-      <c r="K21" t="n">
-        <v>64</v>
-      </c>
-      <c r="L21" t="n">
-        <v>15</v>
-      </c>
-      <c r="M21" t="n">
-        <v>13</v>
-      </c>
-      <c r="N21" t="n">
-        <v>11</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>27</v>
-      </c>
-      <c r="R21" t="n">
-        <v>81</v>
-      </c>
       <c r="S21" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.484</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>600:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>250.84</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.649</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.148</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.116</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.256</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.759</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.141</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -3641,157 +3641,157 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>310</v>
+        <v>444</v>
       </c>
       <c r="D22" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E22" t="n">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="F22" t="n">
+        <v>56</v>
+      </c>
+      <c r="G22" t="n">
+        <v>137</v>
+      </c>
+      <c r="H22" t="n">
+        <v>76</v>
+      </c>
+      <c r="I22" t="n">
+        <v>90</v>
+      </c>
+      <c r="J22" t="n">
+        <v>84</v>
+      </c>
+      <c r="K22" t="n">
+        <v>99</v>
+      </c>
+      <c r="L22" t="n">
+        <v>36</v>
+      </c>
+      <c r="M22" t="n">
+        <v>23</v>
+      </c>
+      <c r="N22" t="n">
         <v>20</v>
       </c>
-      <c r="G22" t="n">
-        <v>62</v>
-      </c>
-      <c r="H22" t="n">
-        <v>74</v>
-      </c>
-      <c r="I22" t="n">
-        <v>91</v>
-      </c>
-      <c r="J22" t="n">
-        <v>52</v>
-      </c>
-      <c r="K22" t="n">
-        <v>84</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>44</v>
+      </c>
+      <c r="R22" t="n">
+        <v>122</v>
+      </c>
+      <c r="S22" t="n">
+        <v>109</v>
+      </c>
+      <c r="T22" t="n">
+        <v>462</v>
+      </c>
+      <c r="U22" t="n">
+        <v>37</v>
+      </c>
+      <c r="V22" t="n">
+        <v>41</v>
+      </c>
+      <c r="W22" t="n">
         <v>27</v>
       </c>
-      <c r="M22" t="n">
+      <c r="X22" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>76</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="AB22" t="n">
         <v>17</v>
       </c>
-      <c r="N22" t="n">
-        <v>12</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>20</v>
-      </c>
-      <c r="R22" t="n">
-        <v>67</v>
-      </c>
-      <c r="S22" t="n">
-        <v>81</v>
-      </c>
-      <c r="T22" t="n">
-        <v>386</v>
-      </c>
-      <c r="U22" t="n">
-        <v>29</v>
-      </c>
-      <c r="V22" t="n">
-        <v>29</v>
-      </c>
-      <c r="W22" t="n">
-        <v>25</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="AC22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>68</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="AH22" t="n">
         <v>17</v>
       </c>
-      <c r="Y22" t="n">
-        <v>69</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>86</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.802</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC22" t="n">
+      <c r="AI22" t="n">
         <v>31</v>
       </c>
-      <c r="AD22" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>14</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>0.429</v>
+        <v>0.548</v>
       </c>
       <c r="AK22" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="AL22" t="n">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.292</v>
+        <v>0.368</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>600:00</t>
+          <t>1000:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>261.04</v>
+        <v>412.6</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.599</v>
+        <v>0.57</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.654</v>
+        <v>0.612</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.188</v>
+        <v>1.076</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.092</v>
+        <v>0.121</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.376</v>
+        <v>0.235</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.167</v>
+        <v>1.68</v>
       </c>
       <c r="AV22" t="n">
         <v>0.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.059</v>
+        <v>0.043</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -3800,1098 +3800,1098 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="inlineStr"/>
+          <t>Rival</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>507</v>
+      </c>
+      <c r="D23" t="n">
+        <v>140</v>
+      </c>
+      <c r="E23" t="n">
+        <v>218</v>
+      </c>
+      <c r="F23" t="n">
+        <v>42</v>
+      </c>
+      <c r="G23" t="n">
+        <v>112</v>
+      </c>
+      <c r="H23" t="n">
+        <v>101</v>
+      </c>
+      <c r="I23" t="n">
+        <v>124</v>
+      </c>
+      <c r="J23" t="n">
+        <v>85</v>
+      </c>
+      <c r="K23" t="n">
+        <v>133</v>
+      </c>
+      <c r="L23" t="n">
+        <v>53</v>
+      </c>
+      <c r="M23" t="n">
+        <v>27</v>
+      </c>
+      <c r="N23" t="n">
+        <v>22</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>37</v>
+      </c>
+      <c r="R23" t="n">
+        <v>109</v>
+      </c>
+      <c r="S23" t="n">
+        <v>118</v>
+      </c>
+      <c r="T23" t="n">
+        <v>623</v>
+      </c>
+      <c r="U23" t="n">
+        <v>46</v>
+      </c>
+      <c r="V23" t="n">
+        <v>56</v>
+      </c>
+      <c r="W23" t="n">
+        <v>32</v>
+      </c>
+      <c r="X23" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>86</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>109</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>61</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>92</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>1000:00</t>
+        </is>
+      </c>
+      <c r="AO23" t="n">
+        <v>426.56</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.189</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>#3 J. FERNÁNDEZ (Per Game)</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>3</v>
-      </c>
-      <c r="C24" t="n">
-        <v>13</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="T24" t="n">
-        <v>42</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AO24" t="n">
-        <v>11.093</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.172</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0.115</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>#4 W. VAN BECK (Per Game)</t>
+          <t>#3 J. FERNÁNDEZ (Per Game)</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>55</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL25" t="n">
         <v>3</v>
       </c>
-      <c r="C25" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="G25" t="n">
-        <v>4</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="AM25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AO25" t="n">
+        <v>9.032</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AU25" t="n">
         <v>2.667</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="T25" t="n">
-        <v>10</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AO25" t="n">
-        <v>8.507</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0.618</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0.6820000000000001</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.097</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
       <c r="AV25" t="n">
-        <v>0.306</v>
+        <v>0.231</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.03</v>
+        <v>0.013</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.033</v>
+        <v>0.139</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>#9 M. HUERTAS (Per Game)</t>
+          <t>#4 W. VAN BECK (Per Game)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>1.667</v>
+        <v>1.2</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="I26" t="n">
-        <v>1.333</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="M26" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.333</v>
+        <v>2.6</v>
       </c>
       <c r="S26" t="n">
-        <v>1.667</v>
+        <v>1.2</v>
       </c>
       <c r="T26" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="U26" t="n">
-        <v>2.667</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.667</v>
+        <v>0.4</v>
       </c>
       <c r="W26" t="n">
-        <v>0.333</v>
+        <v>1.2</v>
       </c>
       <c r="X26" t="n">
-        <v>0.333</v>
+        <v>0.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.333</v>
+        <v>0.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.667</v>
+        <v>0.6</v>
       </c>
       <c r="AL26" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.417</v>
+        <v>0.25</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>10.253</v>
+        <v>7.168</v>
       </c>
       <c r="AP26" t="n">
         <v>0.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.522</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.975</v>
+        <v>0.977</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.065</v>
+        <v>0.14</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.111</v>
+        <v>0.346</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.5</v>
+        <v>0.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.23</v>
+        <v>0.241</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.038</v>
+        <v>0.033</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.062</v>
+        <v>0.091</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.17</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#10 E. FRIDRIKSSON (Per Game)</t>
+          <t>#9 M. HUERTAS (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D27" t="n">
         <v>3</v>
       </c>
-      <c r="C27" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.667</v>
-      </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
-        <v>1.667</v>
+        <v>4.6</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.667</v>
+        <v>1.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.667</v>
+        <v>1.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.333</v>
+        <v>1.6</v>
       </c>
       <c r="S27" t="n">
-        <v>0.667</v>
+        <v>2.2</v>
       </c>
       <c r="T27" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.333</v>
+        <v>0.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.333</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.667</v>
+        <v>4.4</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.667</v>
+        <v>2.8</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>2.667</v>
+        <v>11.704</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.333</v>
+        <v>0.459</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.333</v>
+        <v>0.495</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.5</v>
+        <v>0.889</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.25</v>
+        <v>0.103</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AU27" t="n">
-        <v>2.5</v>
+        <v>3.833</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.165</v>
+        <v>0.275</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.171</v>
+        <v>0.064</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.052</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#11 T. SCRUBB (Per Game)</t>
+          <t>#10 E. FRIDRIKSSON (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T28" t="n">
         <v>5</v>
       </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG28" t="n">
         <v>0.333</v>
       </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="T28" t="n">
-        <v>25</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
       <c r="AH28" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.333</v>
+        <v>0.6</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>25:43</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>4.667</v>
+        <v>2.6</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.577</v>
+        <v>0.222</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.577</v>
+        <v>0.222</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.071</v>
+        <v>0.308</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.308</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.188</v>
+        <v>0.108</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.054</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#15 J. SASTRE (Per Game)</t>
+          <t>#11 T. SCRUBB (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="D29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>51</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>0.667</v>
       </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>13</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1</v>
-      </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.667</v>
+        <v>1.4</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>26:35</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>2.627</v>
+        <v>5.2</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.583</v>
+        <v>0.783</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.654</v>
+        <v>0.783</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.142</v>
+        <v>1.385</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.127</v>
+        <v>0.115</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
         <v>2</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.096</v>
+        <v>0.095</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.234</v>
+        <v>0.129</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.021</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#16 D. BORDÓN (Per Game)</t>
+          <t>#15 J. SASTRE (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T30" t="n">
+        <v>14</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA30" t="n">
         <v>0.667</v>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
@@ -4911,106 +4911,106 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.333</v>
+        <v>0.6</v>
       </c>
       <c r="AM30" t="n">
         <v>0</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>0.96</v>
+        <v>1.776</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.347</v>
+        <v>0.571</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.694</v>
+        <v>1.014</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>0.113</v>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>0.286</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.366</v>
+        <v>0.077</v>
       </c>
       <c r="AW30" t="n">
         <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>0.189</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#21 T. ABROMAITIS (Per Game)</t>
+          <t>#16 D. BORDÓN (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>0.667</v>
       </c>
       <c r="D31" t="n">
-        <v>2.333</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>4.667</v>
+        <v>0.333</v>
       </c>
       <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="H31" t="n">
         <v>0.667</v>
       </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1.333</v>
-      </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0.667</v>
       </c>
       <c r="J31" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2.333</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0.333</v>
       </c>
       <c r="N31" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -5022,19 +5022,19 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.667</v>
+        <v>0.333</v>
       </c>
       <c r="S31" t="n">
-        <v>2.333</v>
+        <v>0.333</v>
       </c>
       <c r="T31" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>2.333</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -5043,448 +5043,448 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2</v>
+        <v>0.333</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
         <v>0.333</v>
       </c>
-      <c r="AF31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0.667</v>
-      </c>
       <c r="AM31" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>6.547</v>
+        <v>0.96</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.588</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.611</v>
+        <v>0.347</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.222</v>
+        <v>0.694</v>
       </c>
       <c r="AS31" t="n">
         <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.235</v>
+        <v>1</v>
       </c>
       <c r="AU31" t="n">
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.156</v>
+        <v>0.371</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#25 K. YEBO (Per Game)</t>
+          <t>#21 T. ABROMAITIS (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="C32" t="n">
-        <v>14.667</v>
-      </c>
-      <c r="D32" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="E32" t="n">
-        <v>7.333</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="I32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="J32" t="n">
+      <c r="S32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>37</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD32" t="n">
         <v>0.333</v>
       </c>
-      <c r="K32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4</v>
-      </c>
-      <c r="T32" t="n">
-        <v>47</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="V32" t="n">
+      <c r="AE32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>0.667</v>
       </c>
-      <c r="W32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
       <c r="AK32" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.667</v>
+        <v>1</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>11.613</v>
+        <v>6.88</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.483</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.539</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.263</v>
+        <v>1.047</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.029</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.259</v>
+        <v>0.276</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.333</v>
+        <v>2</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.274</v>
+        <v>0.161</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.02</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.195</v>
+        <v>0.153</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#33 H. ALDERETE (Per Game)</t>
+          <t>#25 K. YEBO (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>12.4</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="F33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T33" t="n">
+        <v>61</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AG33" t="n">
         <v>0.333</v>
       </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
       <c r="AH33" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AO33" t="n">
+        <v>10.656</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.164</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AU33" t="n">
         <v>0.5</v>
       </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AO33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
       <c r="AV33" t="n">
-        <v>0.039</v>
+        <v>0.296</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.108</v>
+        <v>0.166</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#42 A. DOORNEKAMP (Per Game)</t>
+          <t>#33 H. ALDERETE (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>11.667</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="E34" t="n">
-        <v>2.667</v>
+        <v>0.2</v>
       </c>
       <c r="F34" t="n">
-        <v>2.333</v>
+        <v>0.2</v>
       </c>
       <c r="G34" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="H34" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>2.333</v>
+        <v>0.4</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="L34" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="M34" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -5493,157 +5493,157 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="R34" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="S34" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="AD34" t="n">
         <v>1</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.667</v>
+        <v>0.4</v>
       </c>
       <c r="AJ34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
         <v>0.4</v>
       </c>
-      <c r="AK34" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>3.333</v>
-      </c>
       <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AO34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP34" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>27:08</t>
-        </is>
-      </c>
-      <c r="AO34" t="n">
-        <v>8.627000000000001</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0.717</v>
-      </c>
       <c r="AQ34" t="n">
-        <v>0.733</v>
+        <v>0.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.352</v>
+        <v>0.833</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.077</v>
+        <v>0.167</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.152</v>
+        <v>0.062</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.015</v>
+        <v>0.05</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.097</v>
+        <v>0.112</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.081</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#88 P. MILLS (Per Game)</t>
+          <t>#35 F. GUERRA (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
         <v>3</v>
       </c>
-      <c r="C35" t="n">
-        <v>18.333</v>
-      </c>
-      <c r="D35" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="E35" t="n">
-        <v>5.667</v>
-      </c>
       <c r="F35" t="n">
-        <v>2.333</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>4.667</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>4.667</v>
+        <v>2.5</v>
       </c>
       <c r="I35" t="n">
-        <v>4.667</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0.333</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>0.333</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5652,590 +5652,908 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="R35" t="n">
-        <v>2.667</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="T35" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="U35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.667</v>
+        <v>1.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.667</v>
+        <v>2</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="AB35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AO35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AP35" t="n">
         <v>0.667</v>
       </c>
-      <c r="AC35" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AO35" t="n">
-        <v>14.387</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0.661</v>
-      </c>
       <c r="AQ35" t="n">
-        <v>0.74</v>
+        <v>0.793</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.274</v>
+        <v>1.413</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.139</v>
+        <v>0.109</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.452</v>
+        <v>0.833</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.387</v>
+        <v>0.144</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.023</v>
+        <v>0.115</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.025</v>
+        <v>0.17</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>#42 A. DOORNEKAMP (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R36" t="n">
         <v>3</v>
       </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="S36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T36" t="n">
+        <v>42</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AG36" t="n">
         <v>0.667</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>25:07</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>6.952</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>0.629</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>0.656</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.237</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>TOTAL (Per Game)</t>
+          <t>#88 P. MILLS (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" t="n">
+        <v>20</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E37" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F37" t="n">
         <v>3</v>
       </c>
-      <c r="C37" t="n">
+      <c r="G37" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T37" t="n">
         <v>96</v>
       </c>
-      <c r="D37" t="n">
-        <v>19.667</v>
-      </c>
-      <c r="E37" t="n">
-        <v>35.333</v>
-      </c>
-      <c r="F37" t="n">
-        <v>13.333</v>
-      </c>
-      <c r="G37" t="n">
-        <v>29.667</v>
-      </c>
-      <c r="H37" t="n">
-        <v>16.667</v>
-      </c>
-      <c r="I37" t="n">
-        <v>20.333</v>
-      </c>
-      <c r="J37" t="n">
-        <v>17</v>
-      </c>
-      <c r="K37" t="n">
-        <v>21.333</v>
-      </c>
-      <c r="L37" t="n">
-        <v>5</v>
-      </c>
-      <c r="M37" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="N37" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>9</v>
-      </c>
-      <c r="R37" t="n">
-        <v>27</v>
-      </c>
-      <c r="S37" t="n">
-        <v>22.333</v>
-      </c>
-      <c r="T37" t="n">
-        <v>292</v>
-      </c>
       <c r="U37" t="n">
-        <v>9</v>
+        <v>1.8</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>6.333</v>
+        <v>1.2</v>
       </c>
       <c r="X37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF37" t="n">
         <v>3</v>
       </c>
-      <c r="Y37" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>16.667</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>10.333</v>
-      </c>
       <c r="AG37" t="n">
-        <v>0.484</v>
+        <v>0.467</v>
       </c>
       <c r="AH37" t="n">
-        <v>3.333</v>
+        <v>0.8</v>
       </c>
       <c r="AI37" t="n">
-        <v>6.667</v>
+        <v>1.4</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AK37" t="n">
-        <v>10</v>
+        <v>2.2</v>
       </c>
       <c r="AL37" t="n">
-        <v>23</v>
+        <v>4.6</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.435</v>
+        <v>0.478</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>200:00</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>83.613</v>
+        <v>15.736</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.61</v>
+        <v>0.669</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.649</v>
+        <v>0.728</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.148</v>
+        <v>1.271</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.116</v>
+        <v>0.127</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.256</v>
+        <v>0.356</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.759</v>
+        <v>1</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.03</v>
+        <v>0.011</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.141</v>
+        <v>0.048</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
+          <t>Equip (Per Game)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL (Per Game)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="D39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E39" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="H39" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>18</v>
+      </c>
+      <c r="J39" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="K39" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="L39" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="R39" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="T39" t="n">
+        <v>462</v>
+      </c>
+      <c r="U39" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V39" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W39" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>200:00</t>
+        </is>
+      </c>
+      <c r="AO39" t="n">
+        <v>82.52</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
           <t>Rival (Per Game)</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>3</v>
-      </c>
-      <c r="C38" t="n">
-        <v>103.333</v>
-      </c>
-      <c r="D38" t="n">
-        <v>29.333</v>
-      </c>
-      <c r="E38" t="n">
-        <v>45</v>
-      </c>
-      <c r="F38" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="G38" t="n">
-        <v>20.667</v>
-      </c>
-      <c r="H38" t="n">
-        <v>24.667</v>
-      </c>
-      <c r="I38" t="n">
-        <v>30.333</v>
-      </c>
-      <c r="J38" t="n">
-        <v>17.333</v>
-      </c>
-      <c r="K38" t="n">
+      <c r="B40" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="D40" t="n">
         <v>28</v>
       </c>
-      <c r="L38" t="n">
-        <v>9</v>
-      </c>
-      <c r="M38" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="N38" t="n">
+      <c r="E40" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G40" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="H40" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="J40" t="n">
+        <v>17</v>
+      </c>
+      <c r="K40" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="L40" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M40" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="R40" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S40" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="T40" t="n">
+        <v>623</v>
+      </c>
+      <c r="U40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="V40" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W40" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="X40" t="n">
         <v>4</v>
       </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="R38" t="n">
-        <v>22.333</v>
-      </c>
-      <c r="S38" t="n">
-        <v>27</v>
-      </c>
-      <c r="T38" t="n">
-        <v>386</v>
-      </c>
-      <c r="U38" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="V38" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="W38" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="X38" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>28.667</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.802</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>10.333</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>16</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="AN38" t="inlineStr">
+      <c r="Y40" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AN40" t="inlineStr">
         <is>
           <t>200:00</t>
         </is>
       </c>
-      <c r="AO38" t="n">
-        <v>87.01300000000001</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.188</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="AY38" t="n">
+      <c r="AO40" t="n">
+        <v>85.312</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.189</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="AY40" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_La Laguna Tenerife.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_La Laguna Tenerife.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>376.6</v>
+        <v>306.8800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>375.08</v>
+        <v>306</v>
       </c>
       <c r="D2" t="n">
-        <v>118.3747467206996</v>
+        <v>116.0130718954248</v>
       </c>
       <c r="E2" t="n">
-        <v>135.1711634851232</v>
+        <v>133.9869281045752</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5696594427244582</v>
+        <v>0.5617760617760618</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1211827435773146</v>
+        <v>0.1201634222542658</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2130177514792899</v>
+        <v>0.1884057971014493</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2471042471042471</v>
       </c>
       <c r="J2" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="K2" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="L2" t="n">
         <v>27</v>
       </c>
       <c r="M2" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="N2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="O2" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2586872586872587</v>
       </c>
       <c r="Q2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R2" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="S2" t="n">
-        <v>0.130030959752322</v>
+        <v>0.1274131274131274</v>
       </c>
       <c r="T2" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="U2" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.2007722007722008</v>
       </c>
       <c r="W2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="X2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.09266409266409266</v>
+      </c>
+      <c r="Z2" t="n">
         <v>31</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0.09597523219814241</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>39</v>
-      </c>
       <c r="AA2" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3281733746130031</v>
+        <v>0.3204633204633205</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7236842105263158</v>
+        <v>0.7164179104477612</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4047619047619048</v>
+        <v>0.3939393939393939</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3679245283018868</v>
+        <v>0.3734939759036144</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.447368421052632</v>
+        <v>1.432835820895522</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.226277372262774</v>
+        <v>1.205607476635514</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.8857142857142857</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.138888888888889</v>
+        <v>1.115384615384615</v>
       </c>
       <c r="AM2" t="n">
         <v>1.8</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.68</v>
+        <v>1.625</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.46</v>
+        <v>6.475</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.140000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.32000000000001</v>
+        <v>76.72000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>75.01599999999999</v>
+        <v>76.5</v>
       </c>
       <c r="D3" t="n">
-        <v>118.3747467206996</v>
+        <v>116.0130718954248</v>
       </c>
       <c r="E3" t="n">
-        <v>135.1711634851232</v>
+        <v>133.9869281045752</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5696594427244582</v>
+        <v>0.5617760617760618</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1211827435773146</v>
+        <v>0.1201634222542658</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2130177514792899</v>
+        <v>0.1884057971014493</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2471042471042471</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4</v>
+        <v>7.75</v>
       </c>
       <c r="K3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.25</v>
       </c>
       <c r="L3" t="n">
-        <v>5.4</v>
+        <v>6.75</v>
       </c>
       <c r="M3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>15.2</v>
+        <v>16.75</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2586872586872587</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>8.4</v>
+        <v>8.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0.130030959752322</v>
+        <v>0.1274131274131274</v>
       </c>
       <c r="T3" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="U3" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.2007722007722008</v>
       </c>
       <c r="W3" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="X3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09597523219814243</v>
+        <v>0.09266409266409266</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.8</v>
+        <v>7.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.2</v>
+        <v>20.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3281733746130031</v>
+        <v>0.3204633204633205</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7236842105263158</v>
+        <v>0.7164179104477612</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4047619047619047</v>
+        <v>0.3939393939393939</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3679245283018868</v>
+        <v>0.3734939759036144</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.447368421052632</v>
+        <v>1.432835820895522</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.226277372262774</v>
+        <v>1.205607476635514</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.8857142857142857</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.138888888888889</v>
+        <v>1.115384615384615</v>
       </c>
       <c r="AM3" t="n">
         <v>1.8</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.68</v>
+        <v>1.625</v>
       </c>
       <c r="AO3" t="n">
-        <v>6.459999999999999</v>
+        <v>6.475</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.139999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373.5599999999999</v>
+        <v>305.1199999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>375.08</v>
+        <v>306</v>
       </c>
       <c r="D4" t="n">
-        <v>135.1711634851232</v>
+        <v>133.9869281045752</v>
       </c>
       <c r="E4" t="n">
-        <v>118.3747467206996</v>
+        <v>116.0130718954248</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6151515151515151</v>
+        <v>0.6175373134328358</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09846211552888222</v>
+        <v>0.1011209984976309</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3486842105263158</v>
+        <v>0.3360655737704918</v>
       </c>
       <c r="I4" t="n">
-        <v>0.306060606060606</v>
+        <v>0.2947761194029851</v>
       </c>
       <c r="J4" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="L4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="N4" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="O4" t="n">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3303030303030303</v>
+        <v>0.373134328358209</v>
       </c>
       <c r="Q4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="R4" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1848484848484848</v>
+        <v>0.1865671641791045</v>
       </c>
       <c r="T4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="U4" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1454545454545454</v>
+        <v>0.1082089552238806</v>
       </c>
       <c r="W4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06060606060606061</v>
+        <v>0.05970149253731343</v>
       </c>
       <c r="Z4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2787878787878788</v>
+        <v>0.2723880597014925</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7889908256880734</v>
+        <v>0.78</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5245901639344263</v>
+        <v>0.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4482758620689655</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.577981651376147</v>
+        <v>1.56</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.125</v>
+        <v>1.112359550561798</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.056603773584906</v>
+        <v>0.975609756097561</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.6</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.023809523809524</v>
+        <v>2.028571428571428</v>
       </c>
       <c r="AO4" t="n">
-        <v>7.857142857142857</v>
+        <v>7.657142857142857</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.880952380952381</v>
+        <v>9.685714285714285</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.71199999999999</v>
+        <v>76.27999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>75.01599999999999</v>
+        <v>76.5</v>
       </c>
       <c r="D5" t="n">
-        <v>135.1711634851232</v>
+        <v>133.9869281045752</v>
       </c>
       <c r="E5" t="n">
-        <v>118.3747467206996</v>
+        <v>116.0130718954248</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6151515151515152</v>
+        <v>0.6175373134328358</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0984621155288822</v>
+        <v>0.1011209984976309</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3486842105263158</v>
+        <v>0.3360655737704918</v>
       </c>
       <c r="I5" t="n">
-        <v>0.306060606060606</v>
+        <v>0.2947761194029851</v>
       </c>
       <c r="J5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>6.4</v>
+        <v>7.75</v>
       </c>
       <c r="M5" t="n">
-        <v>7.4</v>
+        <v>7.75</v>
       </c>
       <c r="N5" t="n">
-        <v>17.2</v>
+        <v>19.5</v>
       </c>
       <c r="O5" t="n">
-        <v>21.8</v>
+        <v>25</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3303030303030303</v>
+        <v>0.373134328358209</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="R5" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1848484848484848</v>
+        <v>0.1865671641791045</v>
       </c>
       <c r="T5" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="U5" t="n">
-        <v>9.6</v>
+        <v>7.25</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1454545454545454</v>
+        <v>0.1082089552238806</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="X5" t="n">
         <v>4</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06060606060606061</v>
+        <v>0.05970149253731343</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.4</v>
+        <v>18.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2787878787878788</v>
+        <v>0.2723880597014925</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7889908256880733</v>
+        <v>0.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5245901639344263</v>
+        <v>0.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.4583333333333334</v>
+        <v>0.4482758620689655</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3478260869565218</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.577981651376147</v>
+        <v>1.56</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.125</v>
+        <v>1.112359550561798</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.056603773584906</v>
+        <v>0.975609756097561</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.6</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.023809523809524</v>
+        <v>2.028571428571428</v>
       </c>
       <c r="AO5" t="n">
-        <v>7.857142857142857</v>
+        <v>7.657142857142857</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.880952380952381</v>
+        <v>9.685714285714285</v>
       </c>
     </row>
     <row r="7">
@@ -1419,22 +1419,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H8" t="n">
         <v>11</v>
@@ -1443,43 +1443,43 @@
         <v>14</v>
       </c>
       <c r="J8" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1500,75 +1500,75 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
         <v>2</v>
       </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
+      <c r="AG8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
         <v>3</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AJ8" t="n">
         <v>0.333</v>
       </c>
-      <c r="AH8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AK8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.4</v>
+        <v>0.417</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>94:36</t>
+          <t>78:21</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>45.16</v>
+        <v>38.16</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.545</v>
+        <v>0.556</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.6</v>
+        <v>0.618</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.041</v>
+        <v>1.074</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.133</v>
+        <v>0.131</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.333</v>
+        <v>0.407</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.667</v>
+        <v>2.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.231</v>
+        <v>0.234</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.139</v>
+        <v>0.117</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.113</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="9">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
         <v>35</v>
@@ -1593,7 +1593,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
@@ -1602,7 +1602,7 @@
         <v>11</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
@@ -1626,7 +1626,7 @@
         <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S9" t="n">
         <v>6</v>
@@ -1677,10 +1677,10 @@
         <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AK9" t="n">
         <v>3</v>
@@ -1693,41 +1693,41 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>72:10</t>
+          <t>62:56</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>35.84</v>
+        <v>34.84</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.586</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.977</v>
+        <v>1.005</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.14</v>
+        <v>0.144</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.346</v>
+        <v>0.36</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.241</v>
+        <v>0.266</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.033</v>
+        <v>0.037</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.091</v>
+        <v>0.104</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.021</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1737,67 +1737,67 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
         <v>8</v>
       </c>
-      <c r="J10" t="n">
-        <v>23</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>8</v>
-      </c>
-      <c r="S10" t="n">
-        <v>11</v>
-      </c>
       <c r="T10" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="U10" t="n">
         <v>8</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
@@ -1809,28 +1809,28 @@
         <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.444</v>
+        <v>0.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.455</v>
+        <v>0.333</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1845,48 +1845,48 @@
         <v>5</v>
       </c>
       <c r="AL10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.357</v>
+        <v>0.417</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>103:12</t>
+          <t>76:53</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>58.52</v>
+        <v>42.64</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.495</v>
+        <v>0.492</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.889</v>
+        <v>0.891</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.103</v>
+        <v>0.094</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.143</v>
+        <v>0.139</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.833</v>
+        <v>3.75</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.275</v>
+        <v>0.267</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.064</v>
+        <v>0.068</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.169</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="11">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
@@ -2036,16 +2036,16 @@
         <v>2</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.172</v>
+        <v>0.17</v>
       </c>
       <c r="AW11" t="n">
         <v>0.032</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.108</v>
+        <v>0.107</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.052</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="12">
@@ -2055,40 +2055,40 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>24</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="C12" t="n">
-        <v>36</v>
-      </c>
-      <c r="D12" t="n">
-        <v>9</v>
-      </c>
-      <c r="E12" t="n">
-        <v>13</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" t="n">
-        <v>10</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
-      </c>
       <c r="K12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
@@ -2103,19 +2103,19 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
         <v>2</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7</v>
       </c>
       <c r="W12" t="n">
         <v>2</v>
@@ -2124,87 +2124,87 @@
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA12" t="n">
         <v>1</v>
       </c>
       <c r="AB12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK12" t="n">
         <v>3</v>
       </c>
-      <c r="AC12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ12" t="n">
+      <c r="AL12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>102:53</t>
+        </is>
+      </c>
+      <c r="AO12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP12" t="n">
         <v>0.667</v>
       </c>
-      <c r="AK12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>132:58</t>
-        </is>
-      </c>
-      <c r="AO12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0.783</v>
-      </c>
       <c r="AQ12" t="n">
-        <v>0.783</v>
+        <v>0.667</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.385</v>
+        <v>1.143</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.115</v>
+        <v>0.143</v>
       </c>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.095</v>
+        <v>0.098</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.129</v>
+        <v>0.14</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="13">
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
@@ -2229,7 +2229,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
@@ -2241,7 +2241,7 @@
         <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2322,48 +2322,48 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>55:48</t>
+          <t>52:11</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>8.880000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.5</v>
+        <v>0.583</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.571</v>
+        <v>0.654</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.014</v>
+        <v>1.142</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.113</v>
+        <v>0.127</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AU13" t="n">
         <v>2</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.077</v>
+        <v>0.073</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.189</v>
+        <v>0.176</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="14">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.371</v>
+        <v>0.368</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -2532,22 +2532,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
         <v>8</v>
@@ -2559,10 +2559,10 @@
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
@@ -2580,13 +2580,13 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="U15" t="n">
         <v>2</v>
@@ -2601,31 +2601,31 @@
         <v>2</v>
       </c>
       <c r="Y15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.625</v>
+        <v>0.571</v>
       </c>
       <c r="AB15" t="n">
         <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.143</v>
+        <v>0.2</v>
       </c>
       <c r="AH15" t="n">
         <v>2</v>
@@ -2637,51 +2637,51 @@
         <v>0.667</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>103:25</t>
+          <t>80:28</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>34.4</v>
+        <v>28.4</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.483</v>
+        <v>0.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.539</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.047</v>
+        <v>1.092</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.029</v>
+        <v>0.035</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.276</v>
+        <v>0.348</v>
       </c>
       <c r="AU15" t="n">
         <v>2</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.161</v>
+        <v>0.17</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.153</v>
+        <v>0.179</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.014</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="16">
@@ -2691,16 +2691,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
@@ -2712,7 +2712,7 @@
         <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J16" t="n">
         <v>2</v>
@@ -2721,28 +2721,28 @@
         <v>11</v>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
+        <v>10</v>
+      </c>
+      <c r="S16" t="n">
         <v>13</v>
-      </c>
-      <c r="S16" t="n">
-        <v>14</v>
       </c>
       <c r="T16" t="n">
         <v>61</v>
@@ -2760,13 +2760,13 @@
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.875</v>
+        <v>0.87</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2806,41 +2806,41 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>87:21</t>
+          <t>81:02</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>53.28</v>
+        <v>50.84</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.625</v>
+        <v>0.616</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.629</v>
+        <v>0.627</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.164</v>
+        <v>1.18</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.075</v>
+        <v>0.059</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.159</v>
+        <v>0.163</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.296</v>
+        <v>0.302</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.081</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.166</v>
+        <v>0.178</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
         <v>5</v>
@@ -2990,16 +2990,16 @@
         <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="AX17" t="n">
         <v>0.112</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="18">
@@ -3009,64 +3009,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
         <v>4</v>
       </c>
-      <c r="E18" t="n">
-        <v>6</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>5</v>
-      </c>
-      <c r="I18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>22</v>
-      </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3078,22 +3078,22 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3124,41 +3124,41 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>30:53</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>9.199999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.793</v>
+        <v>1.042</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.413</v>
+        <v>2.083</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="AU18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.144</v>
+        <v>0.096</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.115</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.17</v>
+        <v>0.183</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3168,37 +3168,37 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
         <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" t="n">
         <v>8</v>
       </c>
-      <c r="K19" t="n">
-        <v>12</v>
-      </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
@@ -3216,19 +3216,19 @@
         <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="U19" t="n">
         <v>5</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>8</v>
@@ -3237,10 +3237,10 @@
         <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
         <v>1</v>
@@ -3276,48 +3276,48 @@
         <v>5</v>
       </c>
       <c r="AL19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.357</v>
+        <v>0.455</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>125:37</t>
+          <t>98:35</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>34.76</v>
+        <v>29.88</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.629</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.656</v>
+        <v>0.699</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.237</v>
+        <v>1.305</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.058</v>
+        <v>0.067</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.129</v>
+        <v>0.074</v>
       </c>
       <c r="AU19" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.134</v>
+        <v>0.146</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.019</v>
+        <v>0.012</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.126</v>
+        <v>0.106</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.057</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="20">
@@ -3327,61 +3327,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="D20" t="n">
+        <v>13</v>
+      </c>
+      <c r="E20" t="n">
+        <v>22</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>15</v>
+      </c>
+      <c r="H20" t="n">
         <v>17</v>
       </c>
-      <c r="E20" t="n">
-        <v>29</v>
-      </c>
-      <c r="F20" t="n">
-        <v>15</v>
-      </c>
-      <c r="G20" t="n">
-        <v>30</v>
-      </c>
-      <c r="H20" t="n">
-        <v>21</v>
-      </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
+        <v>8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>8</v>
+      </c>
+      <c r="R20" t="n">
         <v>10</v>
       </c>
-      <c r="K20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>10</v>
-      </c>
-      <c r="R20" t="n">
-        <v>12</v>
-      </c>
       <c r="S20" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="T20" t="n">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="U20" t="n">
         <v>9</v>
@@ -3396,87 +3396,87 @@
         <v>4</v>
       </c>
       <c r="Y20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK20" t="n">
         <v>6</v>
       </c>
-      <c r="Z20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>11</v>
-      </c>
       <c r="AL20" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.478</v>
+        <v>0.5</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>108:59</t>
+          <t>74:09</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>78.68000000000001</v>
+        <v>52.92</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.669</v>
+        <v>0.635</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.728</v>
+        <v>0.712</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.271</v>
+        <v>1.209</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.127</v>
+        <v>0.151</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.356</v>
+        <v>0.459</v>
       </c>
       <c r="AU20" t="n">
         <v>1</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.35</v>
+        <v>0.343</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.048</v>
+        <v>0.018</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.081</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="21">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -3528,13 +3528,13 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -3645,67 +3645,67 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>444</v>
+        <v>355</v>
       </c>
       <c r="D22" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="E22" t="n">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="F22" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="G22" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="H22" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I22" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J22" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="K22" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="L22" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="M22" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N22" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q22" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R22" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="S22" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="T22" t="n">
-        <v>462</v>
+        <v>365</v>
       </c>
       <c r="U22" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="V22" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="W22" t="n">
         <v>27</v>
@@ -3714,84 +3714,84 @@
         <v>15</v>
       </c>
       <c r="Y22" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Z22" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.724</v>
+        <v>0.716</v>
       </c>
       <c r="AB22" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AC22" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.405</v>
+        <v>0.394</v>
       </c>
       <c r="AE22" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AF22" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.412</v>
+        <v>0.385</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK22" t="n">
         <v>31</v>
       </c>
-      <c r="AJ22" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>39</v>
-      </c>
       <c r="AL22" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.368</v>
+        <v>0.373</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>1000:00</t>
+          <t>800:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>412.6</v>
+        <v>332.88</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.57</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.612</v>
+        <v>0.606</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.076</v>
+        <v>1.066</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.235</v>
+        <v>0.247</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.68</v>
+        <v>1.625</v>
       </c>
       <c r="AV22" t="n">
         <v>0.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.043</v>
+        <v>0.038</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.13</v>
+        <v>0.133</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -3804,153 +3804,153 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>507</v>
+        <v>410</v>
       </c>
       <c r="D23" t="n">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="E23" t="n">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="F23" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G23" t="n">
+        <v>89</v>
+      </c>
+      <c r="H23" t="n">
+        <v>79</v>
+      </c>
+      <c r="I23" t="n">
+        <v>98</v>
+      </c>
+      <c r="J23" t="n">
+        <v>71</v>
+      </c>
+      <c r="K23" t="n">
         <v>112</v>
       </c>
-      <c r="H23" t="n">
-        <v>101</v>
-      </c>
-      <c r="I23" t="n">
-        <v>124</v>
-      </c>
-      <c r="J23" t="n">
-        <v>85</v>
-      </c>
-      <c r="K23" t="n">
-        <v>133</v>
-      </c>
       <c r="L23" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M23" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="Q23" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="R23" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="S23" t="n">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="T23" t="n">
-        <v>623</v>
+        <v>508</v>
       </c>
       <c r="U23" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="V23" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="W23" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="X23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y23" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="Z23" t="n">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.789</v>
+        <v>0.78</v>
       </c>
       <c r="AB23" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AC23" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.525</v>
+        <v>0.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AF23" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.458</v>
+        <v>0.448</v>
       </c>
       <c r="AH23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AI23" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.5</v>
+        <v>0.438</v>
       </c>
       <c r="AK23" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AL23" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.348</v>
+        <v>0.356</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>1000:00</t>
+          <t>800:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>426.56</v>
+        <v>346.12</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.615</v>
+        <v>0.618</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.659</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.189</v>
+        <v>1.185</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.098</v>
+        <v>0.101</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.306</v>
+        <v>0.295</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.024</v>
+        <v>2.029</v>
       </c>
       <c r="AV23" t="n">
         <v>0.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.157</v>
+        <v>0.162</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -4020,67 +4020,67 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>9.4</v>
+        <v>10.25</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="E25" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G25" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H25" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="T25" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -4089,10 +4089,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA25" t="n">
         <v>0.556</v>
@@ -4101,75 +4101,75 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AG25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>0.333</v>
       </c>
-      <c r="AH25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AK25" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL25" t="n">
         <v>3</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.4</v>
+        <v>0.417</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>9.032</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.545</v>
+        <v>0.556</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.6</v>
+        <v>0.618</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.041</v>
+        <v>1.074</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.133</v>
+        <v>0.131</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.333</v>
+        <v>0.407</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.667</v>
+        <v>2.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.231</v>
+        <v>0.234</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.139</v>
+        <v>0.117</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.113</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="26">
@@ -4179,58 +4179,58 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>8.75</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G26" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="H26" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="I26" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="R26" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="T26" t="n">
         <v>16</v>
@@ -4239,19 +4239,19 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="X26" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AA26" t="n">
         <v>1</v>
@@ -4260,75 +4260,75 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AF26" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AG26" t="n">
         <v>0.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AJ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK26" t="n">
         <v>0.75</v>
       </c>
-      <c r="AK26" t="n">
-        <v>0.6</v>
-      </c>
       <c r="AL26" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AM26" t="n">
         <v>0.25</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>7.168</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.586</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.977</v>
+        <v>1.005</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.14</v>
+        <v>0.144</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.346</v>
+        <v>0.36</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.241</v>
+        <v>0.266</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.033</v>
+        <v>0.037</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.091</v>
+        <v>0.104</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.021</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -4338,40 +4338,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="D27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="E27" t="n">
-        <v>7</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2.8</v>
-      </c>
       <c r="H27" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="N27" t="n">
         <v>1</v>
@@ -4380,58 +4380,58 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="U27" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W27" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="X27" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.444</v>
+        <v>0.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AF27" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.455</v>
+        <v>0.333</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
@@ -4443,51 +4443,51 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.357</v>
+        <v>0.417</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>11.704</v>
+        <v>10.66</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.495</v>
+        <v>0.492</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.889</v>
+        <v>0.891</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.103</v>
+        <v>0.094</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.143</v>
+        <v>0.139</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.833</v>
+        <v>3.75</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.275</v>
+        <v>0.267</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.064</v>
+        <v>0.068</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.169</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="28">
@@ -4497,22 +4497,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -4521,13 +4521,13 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -4539,16 +4539,16 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
         <v>5</v>
@@ -4566,10 +4566,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AA28" t="n">
         <v>0.5</v>
@@ -4584,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AG28" t="n">
         <v>0.333</v>
@@ -4596,7 +4596,7 @@
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
@@ -4605,18 +4605,18 @@
         <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AM28" t="n">
         <v>0</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="AP28" t="n">
         <v>0.222</v>
@@ -4637,16 +4637,16 @@
         <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.172</v>
+        <v>0.17</v>
       </c>
       <c r="AW28" t="n">
         <v>0.032</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.108</v>
+        <v>0.107</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.052</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="29">
@@ -4656,19 +4656,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="E29" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F29" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
@@ -4680,49 +4680,49 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="K29" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="L29" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="N29" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S29" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T29" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="U29" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="X29" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Y29" t="n">
         <v>1</v>
@@ -4734,78 +4734,78 @@
         <v>1</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AJ29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>25:43</t>
+        </is>
+      </c>
+      <c r="AO29" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AP29" t="n">
         <v>0.667</v>
       </c>
-      <c r="AK29" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>26:35</t>
-        </is>
-      </c>
-      <c r="AO29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0.783</v>
-      </c>
       <c r="AQ29" t="n">
-        <v>0.783</v>
+        <v>0.667</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.385</v>
+        <v>1.143</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.115</v>
+        <v>0.143</v>
       </c>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.095</v>
+        <v>0.098</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.129</v>
+        <v>0.14</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="30">
@@ -4815,40 +4815,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K30" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -4857,16 +4857,16 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="R30" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="T30" t="n">
         <v>14</v>
@@ -4884,10 +4884,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AA30" t="n">
         <v>0.667</v>
@@ -4911,10 +4911,10 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AJ30" t="n">
         <v>1</v>
@@ -4923,48 +4923,48 @@
         <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AM30" t="n">
         <v>0</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>1.776</v>
+        <v>1.97</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.5</v>
+        <v>0.583</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.571</v>
+        <v>0.654</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.014</v>
+        <v>1.142</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.113</v>
+        <v>0.127</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.077</v>
+        <v>0.073</v>
       </c>
       <c r="AW30" t="n">
         <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.189</v>
+        <v>0.176</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="31">
@@ -5114,7 +5114,7 @@
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.371</v>
+        <v>0.368</v>
       </c>
       <c r="AW31" t="n">
         <v>0</v>
@@ -5133,156 +5133,156 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>7.2</v>
+        <v>7.75</v>
       </c>
       <c r="D32" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="E32" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="G32" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H32" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K32" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="L32" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="N32" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="R32" t="n">
         <v>3</v>
       </c>
       <c r="S32" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T32" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="U32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD32" t="n">
         <v>0.4</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AE32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG32" t="n">
         <v>0.2</v>
       </c>
-      <c r="AF32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0.143</v>
-      </c>
       <c r="AH32" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AJ32" t="n">
         <v>0.667</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="AL32" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>6.88</v>
+        <v>7.1</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.483</v>
+        <v>0.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.539</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.047</v>
+        <v>1.092</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.029</v>
+        <v>0.035</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.276</v>
+        <v>0.348</v>
       </c>
       <c r="AU32" t="n">
         <v>2</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.161</v>
+        <v>0.17</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.153</v>
+        <v>0.179</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.014</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="33">
@@ -5292,40 +5292,40 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>12.4</v>
+        <v>15</v>
       </c>
       <c r="D33" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="E33" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="G33" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="H33" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K33" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="L33" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="N33" t="n">
         <v>1</v>
@@ -5334,55 +5334,55 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="R33" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S33" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="T33" t="n">
         <v>61</v>
       </c>
       <c r="U33" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="W33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="X33" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Y33" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.875</v>
+        <v>0.87</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AG33" t="n">
         <v>0.333</v>
@@ -5397,51 +5397,51 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AM33" t="n">
         <v>0.429</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>10.656</v>
+        <v>12.71</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.625</v>
+        <v>0.616</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.629</v>
+        <v>0.627</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.164</v>
+        <v>1.18</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.075</v>
+        <v>0.059</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.159</v>
+        <v>0.163</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.296</v>
+        <v>0.302</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.081</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.166</v>
+        <v>0.178</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="34">
@@ -5451,22 +5451,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -5475,13 +5475,13 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -5493,13 +5493,13 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="R34" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -5529,10 +5529,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AD34" t="n">
         <v>1</v>
@@ -5547,10 +5547,10 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AJ34" t="n">
         <v>0.5</v>
@@ -5559,18 +5559,18 @@
         <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AM34" t="n">
         <v>0</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AP34" t="n">
         <v>0.5</v>
@@ -5591,16 +5591,16 @@
         <v>2</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="AX34" t="n">
         <v>0.112</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="35">
@@ -5610,16 +5610,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -5628,22 +5628,22 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5652,22 +5652,22 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5679,22 +5679,22 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -5725,41 +5725,41 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>4.6</v>
+        <v>1.44</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.793</v>
+        <v>1.042</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.413</v>
+        <v>2.083</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.144</v>
+        <v>0.096</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.115</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.17</v>
+        <v>0.183</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -5769,40 +5769,40 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>8.6</v>
+        <v>9.75</v>
       </c>
       <c r="D36" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="F36" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="K36" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -5811,114 +5811,114 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="R36" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="S36" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T36" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="V36" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="X36" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AA36" t="n">
         <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AD36" t="n">
         <v>1</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AG36" t="n">
         <v>0.667</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AJ36" t="n">
         <v>0.333</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.357</v>
+        <v>0.455</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>25:07</t>
+          <t>24:38</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>6.952</v>
+        <v>7.47</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.629</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.656</v>
+        <v>0.699</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.237</v>
+        <v>1.305</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.058</v>
+        <v>0.067</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.129</v>
+        <v>0.074</v>
       </c>
       <c r="AU36" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.134</v>
+        <v>0.146</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.019</v>
+        <v>0.012</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.126</v>
+        <v>0.106</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.057</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="37">
@@ -5928,43 +5928,43 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D37" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="E37" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="G37" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="H37" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="I37" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J37" t="n">
         <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="N37" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5976,108 +5976,108 @@
         <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S37" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="T37" t="n">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="U37" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="W37" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="X37" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.6</v>
+        <v>0.556</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AD37" t="n">
         <v>1</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AF37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL37" t="n">
         <v>3</v>
       </c>
-      <c r="AG37" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AM37" t="n">
-        <v>0.478</v>
+        <v>0.5</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>21:47</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>15.736</v>
+        <v>13.23</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.669</v>
+        <v>0.635</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.728</v>
+        <v>0.712</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.271</v>
+        <v>1.209</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.127</v>
+        <v>0.151</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.356</v>
+        <v>0.459</v>
       </c>
       <c r="AU37" t="n">
         <v>1</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.35</v>
+        <v>0.343</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.048</v>
+        <v>0.018</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.081</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="38">
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -6114,10 +6114,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -6129,13 +6129,13 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -6246,40 +6246,40 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>88.8</v>
+        <v>88.75</v>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
+        <v>20.25</v>
       </c>
       <c r="E39" t="n">
-        <v>37.2</v>
+        <v>38</v>
       </c>
       <c r="F39" t="n">
-        <v>11.2</v>
+        <v>10.75</v>
       </c>
       <c r="G39" t="n">
-        <v>27.4</v>
+        <v>26.75</v>
       </c>
       <c r="H39" t="n">
-        <v>15.2</v>
+        <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>19.25</v>
       </c>
       <c r="J39" t="n">
-        <v>16.8</v>
+        <v>16.25</v>
       </c>
       <c r="K39" t="n">
-        <v>19.8</v>
+        <v>20.25</v>
       </c>
       <c r="L39" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="N39" t="n">
         <v>4</v>
@@ -6291,73 +6291,73 @@
         <v>10</v>
       </c>
       <c r="Q39" t="n">
-        <v>8.800000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="R39" t="n">
-        <v>24.4</v>
+        <v>24</v>
       </c>
       <c r="S39" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="T39" t="n">
-        <v>462</v>
+        <v>365</v>
       </c>
       <c r="U39" t="n">
-        <v>7.4</v>
+        <v>7.75</v>
       </c>
       <c r="V39" t="n">
-        <v>8.199999999999999</v>
+        <v>7.25</v>
       </c>
       <c r="W39" t="n">
-        <v>5.4</v>
+        <v>6.75</v>
       </c>
       <c r="X39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AH39" t="n">
         <v>3</v>
       </c>
-      <c r="Y39" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.724</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AI39" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.548</v>
+        <v>0.5</v>
       </c>
       <c r="AK39" t="n">
-        <v>7.8</v>
+        <v>7.75</v>
       </c>
       <c r="AL39" t="n">
-        <v>21.2</v>
+        <v>20.75</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.368</v>
+        <v>0.373</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
@@ -6365,34 +6365,34 @@
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>82.52</v>
+        <v>83.22</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.57</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.612</v>
+        <v>0.606</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.076</v>
+        <v>1.066</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.235</v>
+        <v>0.247</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.68</v>
+        <v>1.625</v>
       </c>
       <c r="AV39" t="n">
         <v>0.2</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.043</v>
+        <v>0.038</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.13</v>
+        <v>0.133</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -6405,118 +6405,118 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>101.4</v>
+        <v>102.5</v>
       </c>
       <c r="D40" t="n">
+        <v>29</v>
+      </c>
+      <c r="E40" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="G40" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="H40" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="I40" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="K40" t="n">
         <v>28</v>
       </c>
-      <c r="E40" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="F40" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="G40" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="H40" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I40" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="J40" t="n">
-        <v>17</v>
-      </c>
-      <c r="K40" t="n">
-        <v>26.6</v>
-      </c>
       <c r="L40" t="n">
-        <v>10.6</v>
+        <v>10.25</v>
       </c>
       <c r="M40" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="N40" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>8.4</v>
+        <v>8.75</v>
       </c>
       <c r="Q40" t="n">
-        <v>7.4</v>
+        <v>7.75</v>
       </c>
       <c r="R40" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="S40" t="n">
-        <v>23.6</v>
+        <v>24</v>
       </c>
       <c r="T40" t="n">
-        <v>623</v>
+        <v>508</v>
       </c>
       <c r="U40" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="V40" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="W40" t="n">
-        <v>6.4</v>
+        <v>7.75</v>
       </c>
       <c r="X40" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="Y40" t="n">
-        <v>17.2</v>
+        <v>19.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>21.8</v>
+        <v>25</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.789</v>
+        <v>0.78</v>
       </c>
       <c r="AB40" t="n">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="AC40" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.525</v>
+        <v>0.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="AF40" t="n">
-        <v>9.6</v>
+        <v>7.25</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.458</v>
+        <v>0.448</v>
       </c>
       <c r="AH40" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AI40" t="n">
         <v>4</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.5</v>
+        <v>0.438</v>
       </c>
       <c r="AK40" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="AL40" t="n">
-        <v>18.4</v>
+        <v>18.25</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.348</v>
+        <v>0.356</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
@@ -6524,34 +6524,34 @@
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>85.312</v>
+        <v>86.53</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.615</v>
+        <v>0.618</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.659</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.189</v>
+        <v>1.185</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.098</v>
+        <v>0.101</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.306</v>
+        <v>0.295</v>
       </c>
       <c r="AU40" t="n">
-        <v>2.024</v>
+        <v>2.029</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.207</v>
+        <v>0.208</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.063</v>
+        <v>0.059</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.175</v>
+        <v>0.184</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>

--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_La Laguna Tenerife.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_La Laguna Tenerife.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>306.8800000000001</v>
+        <v>451.2</v>
       </c>
       <c r="C2" t="n">
-        <v>306</v>
+        <v>448.88</v>
       </c>
       <c r="D2" t="n">
-        <v>116.0130718954248</v>
+        <v>115.843878096596</v>
       </c>
       <c r="E2" t="n">
-        <v>133.9869281045752</v>
+        <v>131.8837996792016</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5617760617760618</v>
+        <v>0.5581395348837209</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1201634222542658</v>
+        <v>0.1252019386106624</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1884057971014493</v>
+        <v>0.2167487684729064</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2471042471042471</v>
+        <v>0.227390180878553</v>
       </c>
       <c r="J2" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="L2" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M2" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="N2" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="O2" t="n">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2586872586872587</v>
+        <v>0.2428940568475452</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R2" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1274131274131274</v>
+        <v>0.1369509043927649</v>
       </c>
       <c r="T2" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="U2" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2007722007722008</v>
+        <v>0.2118863049095607</v>
       </c>
       <c r="W2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="X2" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09266409266409266</v>
+        <v>0.09043927648578812</v>
       </c>
       <c r="Z2" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="AA2" t="n">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3204633204633205</v>
+        <v>0.3178294573643411</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7164179104477612</v>
+        <v>0.7127659574468085</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.4150943396226415</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5</v>
+        <v>0.5142857142857142</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3734939759036144</v>
+        <v>0.3577235772357724</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.432835820895522</v>
+        <v>1.425531914893617</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8292682926829268</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.205607476635514</v>
+        <v>1.177215189873418</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.115384615384615</v>
+        <v>1.068181818181818</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.8</v>
+        <v>1.941176470588235</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.625</v>
+        <v>1.548387096774194</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.475</v>
+        <v>6.241935483870968</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.1</v>
+        <v>7.790322580645161</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76.72000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="C3" t="n">
-        <v>76.5</v>
+        <v>74.81333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>116.0130718954248</v>
+        <v>115.843878096596</v>
       </c>
       <c r="E3" t="n">
-        <v>133.9869281045752</v>
+        <v>131.8837996792016</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5617760617760618</v>
+        <v>0.5581395348837209</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1201634222542658</v>
+        <v>0.1252019386106624</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1884057971014493</v>
+        <v>0.2167487684729064</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2471042471042471</v>
+        <v>0.2273901808785529</v>
       </c>
       <c r="J3" t="n">
-        <v>7.75</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>7.25</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="M3" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="O3" t="n">
-        <v>16.75</v>
+        <v>15.66666666666667</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2586872586872587</v>
+        <v>0.2428940568475452</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="R3" t="n">
-        <v>8.25</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1274131274131274</v>
+        <v>0.1369509043927649</v>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="U3" t="n">
-        <v>13</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2007722007722008</v>
+        <v>0.2118863049095607</v>
       </c>
       <c r="W3" t="n">
         <v>3</v>
       </c>
       <c r="X3" t="n">
-        <v>6</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09266409266409266</v>
+        <v>0.0904392764857881</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.75</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.75</v>
+        <v>20.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3204633204633205</v>
+        <v>0.3178294573643411</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7164179104477612</v>
+        <v>0.7127659574468085</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.4150943396226415</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5</v>
+        <v>0.5142857142857143</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3734939759036144</v>
+        <v>0.3577235772357724</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.432835820895522</v>
+        <v>1.425531914893617</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8292682926829269</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.205607476635514</v>
+        <v>1.177215189873418</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.115384615384615</v>
+        <v>1.068181818181818</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.8</v>
+        <v>1.941176470588235</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.625</v>
+        <v>1.548387096774194</v>
       </c>
       <c r="AO3" t="n">
-        <v>6.475</v>
+        <v>6.241935483870967</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.1</v>
+        <v>7.790322580645161</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>305.1199999999999</v>
+        <v>446.5599999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>306</v>
+        <v>448.88</v>
       </c>
       <c r="D4" t="n">
-        <v>133.9869281045752</v>
+        <v>131.8837996792016</v>
       </c>
       <c r="E4" t="n">
-        <v>116.0130718954248</v>
+        <v>115.843878096596</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6175373134328358</v>
+        <v>0.6119791666666666</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1011209984976309</v>
+        <v>0.1142722042714162</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3360655737704918</v>
+        <v>0.3426966292134832</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2947761194029851</v>
+        <v>0.3177083333333333</v>
       </c>
       <c r="J4" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="K4" t="n">
+        <v>68</v>
+      </c>
+      <c r="L4" t="n">
+        <v>34</v>
+      </c>
+      <c r="M4" t="n">
+        <v>52</v>
+      </c>
+      <c r="N4" t="n">
+        <v>100</v>
+      </c>
+      <c r="O4" t="n">
+        <v>134</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.3489583333333333</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>32</v>
+      </c>
+      <c r="R4" t="n">
+        <v>65</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1692708333333333</v>
+      </c>
+      <c r="T4" t="n">
+        <v>25</v>
+      </c>
+      <c r="U4" t="n">
+        <v>52</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1354166666666667</v>
+      </c>
+      <c r="W4" t="n">
+        <v>12</v>
+      </c>
+      <c r="X4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.05989583333333334</v>
+      </c>
+      <c r="Z4" t="n">
         <v>40</v>
       </c>
-      <c r="L4" t="n">
-        <v>31</v>
-      </c>
-      <c r="M4" t="n">
-        <v>31</v>
-      </c>
-      <c r="N4" t="n">
-        <v>78</v>
-      </c>
-      <c r="O4" t="n">
-        <v>100</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.373134328358209</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>25</v>
-      </c>
-      <c r="R4" t="n">
-        <v>50</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.1865671641791045</v>
-      </c>
-      <c r="T4" t="n">
-        <v>13</v>
-      </c>
-      <c r="U4" t="n">
-        <v>29</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.1082089552238806</v>
-      </c>
-      <c r="W4" t="n">
-        <v>7</v>
-      </c>
-      <c r="X4" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.05970149253731343</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>26</v>
-      </c>
       <c r="AA4" t="n">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2723880597014925</v>
+        <v>0.2864583333333333</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.78</v>
+        <v>0.746268656716418</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5</v>
+        <v>0.4923076923076923</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4482758620689655</v>
+        <v>0.4807692307692308</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4375</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3561643835616438</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.56</v>
+        <v>1.492537313432836</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.112359550561798</v>
+        <v>1.172932330827068</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.9</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.975609756097561</v>
+        <v>1.114754098360656</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.631578947368421</v>
+        <v>1.619047619047619</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.028571428571428</v>
+        <v>1.724137931034483</v>
       </c>
       <c r="AO4" t="n">
-        <v>7.657142857142857</v>
+        <v>6.620689655172414</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.685714285714285</v>
+        <v>8.344827586206897</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76.27999999999999</v>
+        <v>74.42666666666666</v>
       </c>
       <c r="C5" t="n">
-        <v>76.5</v>
+        <v>74.81333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>133.9869281045752</v>
+        <v>131.8837996792016</v>
       </c>
       <c r="E5" t="n">
-        <v>116.0130718954248</v>
+        <v>115.843878096596</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6175373134328358</v>
+        <v>0.6119791666666667</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1011209984976309</v>
+        <v>0.1142722042714162</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3360655737704918</v>
+        <v>0.3426966292134832</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2947761194029851</v>
+        <v>0.3177083333333333</v>
       </c>
       <c r="J5" t="n">
         <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="L5" t="n">
-        <v>7.75</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="M5" t="n">
-        <v>7.75</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="N5" t="n">
-        <v>19.5</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="O5" t="n">
-        <v>25</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="P5" t="n">
-        <v>0.373134328358209</v>
+        <v>0.3489583333333333</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.25</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="R5" t="n">
-        <v>12.5</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1865671641791045</v>
+        <v>0.1692708333333333</v>
       </c>
       <c r="T5" t="n">
-        <v>3.25</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="U5" t="n">
-        <v>7.25</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1082089552238806</v>
+        <v>0.1354166666666667</v>
       </c>
       <c r="W5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05970149253731343</v>
+        <v>0.05989583333333334</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.25</v>
+        <v>18.33333333333333</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2723880597014925</v>
+        <v>0.2864583333333333</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.78</v>
+        <v>0.746268656716418</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5</v>
+        <v>0.4923076923076923</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.4482758620689655</v>
+        <v>0.4807692307692308</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4375</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3561643835616438</v>
+        <v>0.3636363636363637</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.56</v>
+        <v>1.492537313432836</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9615384615384617</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.112359550561798</v>
+        <v>1.172932330827068</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.9</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.975609756097561</v>
+        <v>1.114754098360656</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.631578947368421</v>
+        <v>1.619047619047619</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.028571428571428</v>
+        <v>1.724137931034483</v>
       </c>
       <c r="AO5" t="n">
-        <v>7.657142857142857</v>
+        <v>6.620689655172415</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.685714285714285</v>
+        <v>8.344827586206897</v>
       </c>
     </row>
     <row r="7">
@@ -1419,156 +1419,156 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>53</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>21</v>
+      </c>
+      <c r="H8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I8" t="n">
+        <v>18</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" t="n">
         <v>4</v>
       </c>
-      <c r="C8" t="n">
-        <v>41</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="Q8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" t="n">
-        <v>15</v>
-      </c>
-      <c r="H8" t="n">
-        <v>11</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="R8" t="n">
         <v>14</v>
       </c>
-      <c r="J8" t="n">
+      <c r="S8" t="n">
+        <v>16</v>
+      </c>
+      <c r="T8" t="n">
+        <v>60</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z8" t="n">
         <v>13</v>
       </c>
-      <c r="K8" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="AA8" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI8" t="n">
         <v>4</v>
       </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>9</v>
-      </c>
-      <c r="S8" t="n">
-        <v>13</v>
-      </c>
-      <c r="T8" t="n">
-        <v>48</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG8" t="n">
+      <c r="AJ8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI8" t="n">
+      <c r="AK8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>110:35</t>
+        </is>
+      </c>
+      <c r="AO8" t="n">
+        <v>53.92</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AU8" t="n">
         <v>3</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>78:21</t>
-        </is>
-      </c>
-      <c r="AO8" t="n">
-        <v>38.16</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0.618</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.074</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AV8" t="n">
-        <v>0.234</v>
+        <v>0.236</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.117</v>
+        <v>0.134</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.116</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="9">
@@ -1578,37 +1578,37 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>45</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>18</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="n">
+        <v>14</v>
+      </c>
+      <c r="J9" t="n">
         <v>4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>35</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" t="n">
-        <v>15</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9</v>
-      </c>
-      <c r="I9" t="n">
-        <v>11</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1620,19 +1620,19 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1647,10 +1647,10 @@
         <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
         <v>1</v>
@@ -1665,69 +1665,69 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="AH9" t="n">
         <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AK9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.25</v>
+        <v>0.308</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>62:56</t>
+          <t>90:37</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>34.84</v>
+        <v>42.16</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.586</v>
+        <v>0.622</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.005</v>
+        <v>1.067</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.144</v>
+        <v>0.142</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.2</v>
+        <v>0.667</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.266</v>
+        <v>0.225</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.037</v>
+        <v>0.039</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.104</v>
+        <v>0.074</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="10">
@@ -1737,156 +1737,156 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>69</v>
+      </c>
+      <c r="D10" t="n">
+        <v>21</v>
+      </c>
+      <c r="E10" t="n">
+        <v>47</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J10" t="n">
+        <v>29</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
         <v>4</v>
       </c>
-      <c r="C10" t="n">
-        <v>38</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>10</v>
+      </c>
+      <c r="R10" t="n">
         <v>9</v>
       </c>
-      <c r="E10" t="n">
-        <v>24</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="S10" t="n">
+        <v>16</v>
+      </c>
+      <c r="T10" t="n">
+        <v>75</v>
+      </c>
+      <c r="U10" t="n">
         <v>12</v>
       </c>
-      <c r="H10" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="V10" t="n">
+        <v>7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
         <v>6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>15</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>40</v>
-      </c>
-      <c r="U10" t="n">
-        <v>8</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3</v>
       </c>
       <c r="AA10" t="n">
         <v>0.333</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
         <v>6</v>
       </c>
-      <c r="AD10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>5</v>
-      </c>
       <c r="AL10" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.417</v>
+        <v>0.353</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>76:53</t>
+          <t>135:13</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>42.64</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.458</v>
+        <v>0.469</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.492</v>
+        <v>0.504</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.891</v>
+        <v>0.88</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.094</v>
+        <v>0.128</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.139</v>
+        <v>0.141</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.267</v>
+        <v>0.281</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.068</v>
+        <v>0.06</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.136</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="11">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
@@ -2036,16 +2036,16 @@
         <v>2</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.17</v>
+        <v>0.172</v>
       </c>
       <c r="AW11" t="n">
         <v>0.032</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.107</v>
+        <v>0.11</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.066</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="12">
@@ -2055,23 +2055,23 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F12" t="n">
         <v>6</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>10</v>
       </c>
-      <c r="F12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" t="n">
-        <v>8</v>
-      </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
@@ -2079,16 +2079,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3</v>
-      </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
@@ -2103,19 +2103,19 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
         <v>2</v>
@@ -2124,87 +2124,87 @@
         <v>1</v>
       </c>
       <c r="Y12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
         <v>4</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AC12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AK12" t="n">
         <v>4</v>
       </c>
-      <c r="AA12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AL12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>149:06</t>
+        </is>
+      </c>
+      <c r="AO12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
         <v>2</v>
       </c>
-      <c r="AC12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>102:53</t>
-        </is>
-      </c>
-      <c r="AO12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.143</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.667</v>
-      </c>
       <c r="AV12" t="n">
-        <v>0.098</v>
+        <v>0.091</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.034</v>
+        <v>0.04</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.14</v>
+        <v>0.127</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.044</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="13">
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
@@ -2229,7 +2229,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
@@ -2238,13 +2238,13 @@
         <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -2262,13 +2262,13 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -2322,48 +2322,48 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>52:11</t>
+          <t>71:50</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>7.88</v>
+        <v>10.88</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.583</v>
+        <v>0.389</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.654</v>
+        <v>0.455</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.142</v>
+        <v>0.827</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.127</v>
+        <v>0.092</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="AU13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV13" t="n">
         <v>0.073</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.176</v>
+        <v>0.206</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="14">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.368</v>
+        <v>0.371</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -2532,43 +2532,43 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>43</v>
+      </c>
+      <c r="D15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" t="n">
+        <v>25</v>
+      </c>
+      <c r="F15" t="n">
         <v>4</v>
       </c>
-      <c r="C15" t="n">
-        <v>31</v>
-      </c>
-      <c r="D15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" t="n">
-        <v>17</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" t="n">
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2580,13 +2580,13 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T15" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
         <v>2</v>
@@ -2601,31 +2601,31 @@
         <v>2</v>
       </c>
       <c r="Y15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.571</v>
+        <v>0.7</v>
       </c>
       <c r="AB15" t="n">
         <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AE15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.2</v>
+        <v>0.222</v>
       </c>
       <c r="AH15" t="n">
         <v>2</v>
@@ -2637,51 +2637,51 @@
         <v>0.667</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AM15" t="n">
         <v>0.333</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>80:28</t>
+          <t>126:28</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>28.4</v>
+        <v>39.84</v>
       </c>
       <c r="AP15" t="n">
         <v>0.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.554</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.092</v>
+        <v>1.079</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.348</v>
+        <v>0.265</v>
       </c>
       <c r="AU15" t="n">
         <v>2</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.17</v>
+        <v>0.153</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.058</v>
+        <v>0.065</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.179</v>
+        <v>0.16</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.018</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="16">
@@ -2691,67 +2691,67 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E16" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L16" t="n">
+        <v>8</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="n">
         <v>5</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>4</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3</v>
-      </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
+        <v>16</v>
+      </c>
+      <c r="S16" t="n">
+        <v>17</v>
+      </c>
+      <c r="T16" t="n">
+        <v>75</v>
+      </c>
+      <c r="U16" t="n">
         <v>10</v>
       </c>
-      <c r="S16" t="n">
-        <v>13</v>
-      </c>
-      <c r="T16" t="n">
-        <v>61</v>
-      </c>
-      <c r="U16" t="n">
-        <v>6</v>
-      </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W16" t="n">
         <v>2</v>
@@ -2760,28 +2760,28 @@
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Z16" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.87</v>
+        <v>0.862</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG16" t="n">
         <v>0.333</v>
@@ -2790,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
@@ -2799,48 +2799,48 @@
         <v>3</v>
       </c>
       <c r="AL16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>81:02</t>
+          <t>110:23</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>50.84</v>
+        <v>69.48</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.616</v>
+        <v>0.578</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.627</v>
+        <v>0.596</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.18</v>
+        <v>1.123</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.163</v>
+        <v>0.19</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.302</v>
+        <v>0.305</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.178</v>
+        <v>0.183</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.02</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="17">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
         <v>5</v>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>46:58</t>
+          <t>47:01</t>
         </is>
       </c>
       <c r="AO17" t="n">
@@ -2990,16 +2990,16 @@
         <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.112</v>
+        <v>0.115</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="18">
@@ -3009,65 +3009,65 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
+        <v>17</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" t="n">
         <v>3</v>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="n">
+        <v>20</v>
+      </c>
+      <c r="U18" t="n">
         <v>4</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
@@ -3078,28 +3078,28 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1</v>
+        <v>0.714</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -3124,41 +3124,41 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>44:38</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>1.44</v>
+        <v>15.2</v>
       </c>
       <c r="AP18" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.042</v>
+        <v>0.697</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.083</v>
+        <v>1.118</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.096</v>
+        <v>0.165</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.183</v>
+        <v>0.151</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="19">
@@ -3168,82 +3168,82 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>55</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11</v>
+      </c>
+      <c r="G19" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" t="n">
         <v>4</v>
       </c>
-      <c r="C19" t="n">
-        <v>39</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
         <v>8</v>
       </c>
-      <c r="E19" t="n">
-        <v>10</v>
-      </c>
-      <c r="F19" t="n">
-        <v>7</v>
-      </c>
-      <c r="G19" t="n">
-        <v>17</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>7</v>
-      </c>
       <c r="K19" t="n">
+        <v>15</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>19</v>
+      </c>
+      <c r="S19" t="n">
         <v>8</v>
       </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="T19" t="n">
+        <v>56</v>
+      </c>
+      <c r="U19" t="n">
+        <v>8</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" t="n">
         <v>3</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>11</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>38</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>8</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2</v>
-      </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AB19" t="n">
         <v>2</v>
@@ -3264,60 +3264,60 @@
         <v>0.667</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AK19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AL19" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.455</v>
+        <v>0.444</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>98:35</t>
+          <t>145:47</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>29.88</v>
+        <v>41.76</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.699</v>
+        <v>0.709</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.305</v>
+        <v>1.317</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.067</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.074</v>
+        <v>0.108</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.5</v>
+        <v>2.667</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.146</v>
+        <v>0.139</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.012</v>
+        <v>0.032</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.106</v>
+        <v>0.139</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.064</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="20">
@@ -3327,61 +3327,61 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>102</v>
+      </c>
+      <c r="D20" t="n">
+        <v>18</v>
+      </c>
+      <c r="E20" t="n">
+        <v>31</v>
+      </c>
+      <c r="F20" t="n">
+        <v>15</v>
+      </c>
+      <c r="G20" t="n">
+        <v>33</v>
+      </c>
+      <c r="H20" t="n">
+        <v>21</v>
+      </c>
+      <c r="I20" t="n">
+        <v>22</v>
+      </c>
+      <c r="J20" t="n">
+        <v>12</v>
+      </c>
+      <c r="K20" t="n">
         <v>4</v>
       </c>
-      <c r="C20" t="n">
-        <v>64</v>
-      </c>
-      <c r="D20" t="n">
-        <v>13</v>
-      </c>
-      <c r="E20" t="n">
-        <v>22</v>
-      </c>
-      <c r="F20" t="n">
-        <v>7</v>
-      </c>
-      <c r="G20" t="n">
-        <v>15</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="n">
-        <v>18</v>
-      </c>
-      <c r="J20" t="n">
-        <v>8</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
       <c r="L20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="T20" t="n">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="U20" t="n">
         <v>9</v>
@@ -3396,87 +3396,87 @@
         <v>4</v>
       </c>
       <c r="Y20" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB20" t="n">
         <v>5</v>
       </c>
-      <c r="Z20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>3</v>
-      </c>
       <c r="AC20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD20" t="n">
         <v>1</v>
       </c>
       <c r="AE20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF20" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AG20" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AK20" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>74:09</t>
+          <t>130:19</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>52.92</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.635</v>
+        <v>0.633</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.712</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.209</v>
+        <v>1.19</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.151</v>
+        <v>0.14</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.459</v>
+        <v>0.328</v>
       </c>
       <c r="AU20" t="n">
         <v>1</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.343</v>
+        <v>0.319</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.016</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.018</v>
+        <v>0.041</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.077</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="21">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L21" t="n">
         <v>5</v>
@@ -3528,13 +3528,13 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -3645,153 +3645,153 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>355</v>
+        <v>520</v>
       </c>
       <c r="D22" t="n">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="E22" t="n">
-        <v>152</v>
+        <v>229</v>
       </c>
       <c r="F22" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="H22" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="I22" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="J22" t="n">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="K22" t="n">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="L22" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="M22" t="n">
+        <v>29</v>
+      </c>
+      <c r="N22" t="n">
+        <v>25</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>54</v>
+      </c>
+      <c r="R22" t="n">
+        <v>145</v>
+      </c>
+      <c r="S22" t="n">
+        <v>132</v>
+      </c>
+      <c r="T22" t="n">
+        <v>537</v>
+      </c>
+      <c r="U22" t="n">
+        <v>52</v>
+      </c>
+      <c r="V22" t="n">
+        <v>47</v>
+      </c>
+      <c r="W22" t="n">
+        <v>33</v>
+      </c>
+      <c r="X22" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>67</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>94</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>53</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>82</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="AH22" t="n">
         <v>18</v>
       </c>
-      <c r="N22" t="n">
-        <v>16</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>37</v>
-      </c>
-      <c r="R22" t="n">
-        <v>96</v>
-      </c>
-      <c r="S22" t="n">
-        <v>88</v>
-      </c>
-      <c r="T22" t="n">
-        <v>365</v>
-      </c>
-      <c r="U22" t="n">
-        <v>31</v>
-      </c>
-      <c r="V22" t="n">
-        <v>29</v>
-      </c>
-      <c r="W22" t="n">
-        <v>27</v>
-      </c>
-      <c r="X22" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>67</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>33</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.394</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>52</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>12</v>
-      </c>
       <c r="AI22" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.5</v>
+        <v>0.514</v>
       </c>
       <c r="AK22" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="AL22" t="n">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.373</v>
+        <v>0.358</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>800:00</t>
+          <t>1200:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>332.88</v>
+        <v>495.2</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.606</v>
+        <v>0.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.066</v>
+        <v>1.05</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.247</v>
+        <v>0.227</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.625</v>
+        <v>1.548</v>
       </c>
       <c r="AV22" t="n">
         <v>0.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.038</v>
+        <v>0.043</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.133</v>
+        <v>0.131</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -3804,153 +3804,153 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>410</v>
+        <v>592</v>
       </c>
       <c r="D23" t="n">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="E23" t="n">
-        <v>179</v>
+        <v>251</v>
       </c>
       <c r="F23" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="H23" t="n">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="I23" t="n">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="J23" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="K23" t="n">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="L23" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="M23" t="n">
+        <v>35</v>
+      </c>
+      <c r="N23" t="n">
+        <v>27</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>52</v>
+      </c>
+      <c r="R23" t="n">
+        <v>132</v>
+      </c>
+      <c r="S23" t="n">
+        <v>140</v>
+      </c>
+      <c r="T23" t="n">
+        <v>722</v>
+      </c>
+      <c r="U23" t="n">
+        <v>54</v>
+      </c>
+      <c r="V23" t="n">
+        <v>68</v>
+      </c>
+      <c r="W23" t="n">
+        <v>34</v>
+      </c>
+      <c r="X23" t="n">
         <v>21</v>
       </c>
-      <c r="N23" t="n">
-        <v>18</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>31</v>
-      </c>
-      <c r="R23" t="n">
-        <v>88</v>
-      </c>
-      <c r="S23" t="n">
-        <v>96</v>
-      </c>
-      <c r="T23" t="n">
-        <v>508</v>
-      </c>
-      <c r="U23" t="n">
-        <v>36</v>
-      </c>
-      <c r="V23" t="n">
+      <c r="Y23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>134</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>52</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="AK23" t="n">
         <v>40</v>
       </c>
-      <c r="W23" t="n">
-        <v>31</v>
-      </c>
-      <c r="X23" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>78</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>50</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0.448</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>26</v>
-      </c>
       <c r="AL23" t="n">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.356</v>
+        <v>0.364</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>800:00</t>
+          <t>1200:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>346.12</v>
+        <v>507.56</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.618</v>
+        <v>0.612</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.659</v>
+        <v>0.658</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.185</v>
+        <v>1.166</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.101</v>
+        <v>0.114</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.295</v>
+        <v>0.318</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.029</v>
+        <v>1.724</v>
       </c>
       <c r="AV23" t="n">
         <v>0.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.067</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.162</v>
+        <v>0.157</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -4020,156 +4020,156 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>10.25</v>
+        <v>8.833</v>
       </c>
       <c r="D25" t="n">
-        <v>1.5</v>
+        <v>1.333</v>
       </c>
       <c r="E25" t="n">
+        <v>3.167</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="I25" t="n">
         <v>3</v>
       </c>
-      <c r="F25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I25" t="n">
-        <v>3.5</v>
-      </c>
       <c r="J25" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>1.75</v>
+        <v>1.833</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="T25" t="n">
+        <v>60</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
         <v>0.5</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T25" t="n">
-        <v>48</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AD25" t="n">
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AF25" t="n">
         <v>0.5</v>
       </c>
       <c r="AG25" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH25" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AK25" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AL25" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AO25" t="n">
+        <v>8.987</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AU25" t="n">
         <v>3</v>
       </c>
-      <c r="AM25" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>19:35</t>
-        </is>
-      </c>
-      <c r="AO25" t="n">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0.618</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.074</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AV25" t="n">
-        <v>0.234</v>
+        <v>0.236</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.117</v>
+        <v>0.134</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.116</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="26">
@@ -4179,34 +4179,34 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>8.75</v>
+        <v>7.5</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5</v>
+        <v>1.167</v>
       </c>
       <c r="G26" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>2.75</v>
+        <v>2.333</v>
       </c>
       <c r="J26" t="n">
-        <v>0.25</v>
+        <v>0.667</v>
       </c>
       <c r="K26" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="L26" t="n">
         <v>0.5</v>
@@ -4215,43 +4215,43 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>2.333</v>
       </c>
       <c r="S26" t="n">
-        <v>1.5</v>
+        <v>1.833</v>
       </c>
       <c r="T26" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
         <v>0.5</v>
       </c>
-      <c r="W26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0.75</v>
-      </c>
       <c r="Y26" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="AA26" t="n">
         <v>1</v>
@@ -4260,75 +4260,75 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH26" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AI26" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="AL26" t="n">
-        <v>3</v>
+        <v>2.167</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.25</v>
+        <v>0.308</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>8.710000000000001</v>
+        <v>7.027</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.586</v>
+        <v>0.622</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.005</v>
+        <v>1.067</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.144</v>
+        <v>0.142</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.2</v>
+        <v>0.667</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.266</v>
+        <v>0.225</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.037</v>
+        <v>0.039</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.104</v>
+        <v>0.074</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="27">
@@ -4338,31 +4338,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="D27" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>7.833</v>
       </c>
       <c r="F27" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>2.833</v>
       </c>
       <c r="H27" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.667</v>
       </c>
       <c r="J27" t="n">
-        <v>3.75</v>
+        <v>4.833</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -4371,67 +4371,67 @@
         <v>0.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0.25</v>
+        <v>0.667</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>2.667</v>
       </c>
       <c r="T27" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="U27" t="n">
         <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.25</v>
+        <v>1.167</v>
       </c>
       <c r="W27" t="n">
-        <v>0.25</v>
+        <v>0.667</v>
       </c>
       <c r="X27" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
         <v>0.333</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.5</v>
+        <v>2.167</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.5</v>
+        <v>0.462</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.25</v>
+        <v>2.167</v>
       </c>
       <c r="AF27" t="n">
-        <v>3.75</v>
+        <v>4.667</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.333</v>
+        <v>0.464</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
@@ -4443,51 +4443,51 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AL27" t="n">
-        <v>3</v>
+        <v>2.833</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.417</v>
+        <v>0.353</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>10.66</v>
+        <v>13.067</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.458</v>
+        <v>0.469</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.492</v>
+        <v>0.504</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.891</v>
+        <v>0.88</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.094</v>
+        <v>0.128</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.139</v>
+        <v>0.141</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.267</v>
+        <v>0.281</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.068</v>
+        <v>0.06</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.136</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="28">
@@ -4497,37 +4497,37 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="D28" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="K28" t="n">
         <v>0.5</v>
       </c>
-      <c r="E28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.75</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -4539,16 +4539,16 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="T28" t="n">
         <v>5</v>
@@ -4566,10 +4566,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AA28" t="n">
         <v>0.5</v>
@@ -4584,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AG28" t="n">
         <v>0.333</v>
@@ -4596,7 +4596,7 @@
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
@@ -4605,18 +4605,18 @@
         <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AM28" t="n">
         <v>0</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>3.25</v>
+        <v>2.167</v>
       </c>
       <c r="AP28" t="n">
         <v>0.222</v>
@@ -4637,16 +4637,16 @@
         <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.17</v>
+        <v>0.172</v>
       </c>
       <c r="AW28" t="n">
         <v>0.032</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.107</v>
+        <v>0.11</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.066</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="29">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>6.333</v>
       </c>
       <c r="D29" t="n">
-        <v>1.5</v>
+        <v>1.667</v>
       </c>
       <c r="E29" t="n">
         <v>2.5</v>
@@ -4671,141 +4671,141 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R29" t="n">
         <v>2</v>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="V29" t="n">
-        <v>0.5</v>
+        <v>1.167</v>
       </c>
       <c r="W29" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="X29" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="Y29" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="Z29" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AA29" t="n">
         <v>1</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AC29" t="n">
         <v>1.5</v>
       </c>
       <c r="AD29" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH29" t="n">
         <v>0.333</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0.25</v>
       </c>
       <c r="AI29" t="n">
         <v>0.5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.5</v>
+        <v>1.167</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>25:43</t>
+          <t>24:51</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>5.25</v>
+        <v>4.667</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.667</v>
+        <v>0.76</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.667</v>
+        <v>0.76</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.143</v>
+        <v>1.357</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.143</v>
+        <v>0.107</v>
       </c>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.667</v>
+        <v>2</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.098</v>
+        <v>0.091</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.034</v>
+        <v>0.04</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.14</v>
+        <v>0.127</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.044</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="30">
@@ -4815,40 +4815,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="D30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E30" t="n">
         <v>0.5</v>
       </c>
-      <c r="E30" t="n">
-        <v>0.75</v>
-      </c>
       <c r="F30" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="G30" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="J30" t="n">
         <v>0.5</v>
       </c>
       <c r="K30" t="n">
-        <v>1.75</v>
+        <v>1.833</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="M30" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -4857,19 +4857,19 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="T30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -4884,10 +4884,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Z30" t="n">
         <v>0.5</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0.75</v>
       </c>
       <c r="AA30" t="n">
         <v>0.667</v>
@@ -4911,10 +4911,10 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AJ30" t="n">
         <v>1</v>
@@ -4923,48 +4923,48 @@
         <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.5</v>
+        <v>0.833</v>
       </c>
       <c r="AM30" t="n">
         <v>0</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>1.97</v>
+        <v>1.813</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.583</v>
+        <v>0.389</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.654</v>
+        <v>0.455</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.142</v>
+        <v>0.827</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.127</v>
+        <v>0.092</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="AU30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV30" t="n">
         <v>0.073</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.176</v>
+        <v>0.206</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="31">
@@ -5114,7 +5114,7 @@
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.368</v>
+        <v>0.371</v>
       </c>
       <c r="AW31" t="n">
         <v>0</v>
@@ -5133,156 +5133,156 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>7.75</v>
+        <v>7.167</v>
       </c>
       <c r="D32" t="n">
-        <v>1.75</v>
+        <v>1.833</v>
       </c>
       <c r="E32" t="n">
-        <v>4.25</v>
+        <v>4.167</v>
       </c>
       <c r="F32" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="G32" t="n">
         <v>1.5</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I32" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="K32" t="n">
         <v>2.5</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="T32" t="n">
+        <v>50</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AI32" t="n">
         <v>0.5</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R32" t="n">
-        <v>3</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T32" t="n">
-        <v>34</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0.75</v>
       </c>
       <c r="AJ32" t="n">
         <v>0.667</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AM32" t="n">
         <v>0.333</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>7.1</v>
+        <v>6.64</v>
       </c>
       <c r="AP32" t="n">
         <v>0.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.554</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.092</v>
+        <v>1.079</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.348</v>
+        <v>0.265</v>
       </c>
       <c r="AU32" t="n">
         <v>2</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.17</v>
+        <v>0.153</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.058</v>
+        <v>0.065</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.179</v>
+        <v>0.16</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.018</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="33">
@@ -5292,91 +5292,91 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D33" t="n">
-        <v>5.5</v>
+        <v>4.833</v>
       </c>
       <c r="E33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G33" t="n">
-        <v>1.75</v>
+        <v>1.667</v>
       </c>
       <c r="H33" t="n">
-        <v>1.75</v>
+        <v>1.833</v>
       </c>
       <c r="I33" t="n">
-        <v>2.75</v>
+        <v>2.833</v>
       </c>
       <c r="J33" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="K33" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="L33" t="n">
-        <v>1.25</v>
+        <v>1.333</v>
       </c>
       <c r="M33" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>2.667</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>2.833</v>
       </c>
       <c r="T33" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>1.667</v>
       </c>
       <c r="V33" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="W33" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="X33" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="Y33" t="n">
-        <v>5</v>
+        <v>4.167</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.75</v>
+        <v>4.833</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.87</v>
+        <v>0.862</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.75</v>
+        <v>1.667</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AE33" t="n">
         <v>0.5</v>
@@ -5391,57 +5391,57 @@
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AJ33" t="n">
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>12.71</v>
+        <v>11.58</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.616</v>
+        <v>0.578</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.627</v>
+        <v>0.596</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.18</v>
+        <v>1.123</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.163</v>
+        <v>0.19</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.302</v>
+        <v>0.305</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.178</v>
+        <v>0.183</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.02</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="34">
@@ -5451,22 +5451,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="D34" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="E34" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="F34" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -5475,13 +5475,13 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -5493,13 +5493,13 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="R34" t="n">
-        <v>2</v>
+        <v>1.333</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -5529,10 +5529,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AD34" t="n">
         <v>1</v>
@@ -5547,10 +5547,10 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AJ34" t="n">
         <v>0.5</v>
@@ -5559,18 +5559,18 @@
         <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AM34" t="n">
         <v>0</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP34" t="n">
         <v>0.5</v>
@@ -5591,16 +5591,16 @@
         <v>2</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.112</v>
+        <v>0.115</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="35">
@@ -5610,16 +5610,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>5.667</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>3.333</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -5628,46 +5628,46 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>2.667</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="T35" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5679,28 +5679,28 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>2.333</v>
       </c>
       <c r="AA35" t="n">
-        <v>1</v>
+        <v>0.714</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -5725,41 +5725,41 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>1.44</v>
+        <v>5.067</v>
       </c>
       <c r="AP35" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.042</v>
+        <v>0.697</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.083</v>
+        <v>1.118</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.096</v>
+        <v>0.165</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.183</v>
+        <v>0.151</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="36">
@@ -5769,43 +5769,43 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>9.75</v>
+        <v>9.167</v>
       </c>
       <c r="D36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E36" t="n">
         <v>2</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="K36" t="n">
         <v>2.5</v>
       </c>
-      <c r="F36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G36" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2</v>
-      </c>
       <c r="L36" t="n">
-        <v>0.25</v>
+        <v>0.667</v>
       </c>
       <c r="M36" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5817,49 +5817,49 @@
         <v>0.5</v>
       </c>
       <c r="R36" t="n">
-        <v>2.75</v>
+        <v>3.167</v>
       </c>
       <c r="S36" t="n">
-        <v>1.25</v>
+        <v>1.333</v>
       </c>
       <c r="T36" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="U36" t="n">
-        <v>1.25</v>
+        <v>1.333</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="W36" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="X36" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="Y36" t="n">
         <v>0.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AA36" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AD36" t="n">
         <v>1</v>
       </c>
       <c r="AE36" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="n">
         <v>0.667</v>
@@ -5868,57 +5868,57 @@
         <v>0.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.5</v>
+        <v>1.167</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.25</v>
+        <v>1.333</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.455</v>
+        <v>0.444</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>24:38</t>
+          <t>24:17</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>7.47</v>
+        <v>6.96</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.699</v>
+        <v>0.709</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.305</v>
+        <v>1.317</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.067</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.074</v>
+        <v>0.108</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.5</v>
+        <v>2.667</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.146</v>
+        <v>0.139</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.012</v>
+        <v>0.032</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.106</v>
+        <v>0.139</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.064</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="37">
@@ -5928,43 +5928,43 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D37" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
+        <v>5.167</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G37" t="n">
         <v>5.5</v>
       </c>
-      <c r="F37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G37" t="n">
-        <v>3.75</v>
-      </c>
       <c r="H37" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="I37" t="n">
-        <v>4.5</v>
+        <v>3.667</v>
       </c>
       <c r="J37" t="n">
         <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>0.25</v>
+        <v>0.667</v>
       </c>
       <c r="L37" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="M37" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5976,108 +5976,108 @@
         <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>2.5</v>
+        <v>2.333</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>5.167</v>
       </c>
       <c r="T37" t="n">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="U37" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="W37" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.25</v>
+        <v>1.667</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.556</v>
+        <v>0.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="AD37" t="n">
         <v>1</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.25</v>
+        <v>1.167</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.5</v>
+        <v>2.667</v>
       </c>
       <c r="AG37" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AJ37" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH37" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AK37" t="n">
-        <v>1.5</v>
+        <v>1.833</v>
       </c>
       <c r="AL37" t="n">
-        <v>3</v>
+        <v>4.167</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>13.23</v>
+        <v>14.28</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.635</v>
+        <v>0.633</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.712</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.209</v>
+        <v>1.19</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.151</v>
+        <v>0.14</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.459</v>
+        <v>0.328</v>
       </c>
       <c r="AU37" t="n">
         <v>1</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.343</v>
+        <v>0.319</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.016</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.018</v>
+        <v>0.041</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.077</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="38">
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -6114,10 +6114,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L38" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -6129,13 +6129,13 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.75</v>
+        <v>1.333</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -6246,118 +6246,118 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C39" t="n">
-        <v>88.75</v>
+        <v>86.667</v>
       </c>
       <c r="D39" t="n">
-        <v>20.25</v>
+        <v>20.5</v>
       </c>
       <c r="E39" t="n">
-        <v>38</v>
+        <v>38.167</v>
       </c>
       <c r="F39" t="n">
-        <v>10.75</v>
+        <v>10.333</v>
       </c>
       <c r="G39" t="n">
-        <v>26.75</v>
+        <v>26.333</v>
       </c>
       <c r="H39" t="n">
+        <v>14.667</v>
+      </c>
+      <c r="I39" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J39" t="n">
         <v>16</v>
       </c>
-      <c r="I39" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="J39" t="n">
-        <v>16.25</v>
-      </c>
       <c r="K39" t="n">
-        <v>20.25</v>
+        <v>19.5</v>
       </c>
       <c r="L39" t="n">
-        <v>6.5</v>
+        <v>7.333</v>
       </c>
       <c r="M39" t="n">
-        <v>4.5</v>
+        <v>4.833</v>
       </c>
       <c r="N39" t="n">
-        <v>4</v>
+        <v>4.167</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>10</v>
+        <v>10.333</v>
       </c>
       <c r="Q39" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="R39" t="n">
-        <v>24</v>
+        <v>24.167</v>
       </c>
       <c r="S39" t="n">
         <v>22</v>
       </c>
       <c r="T39" t="n">
-        <v>365</v>
+        <v>537</v>
       </c>
       <c r="U39" t="n">
-        <v>7.75</v>
+        <v>8.667</v>
       </c>
       <c r="V39" t="n">
-        <v>7.25</v>
+        <v>7.833</v>
       </c>
       <c r="W39" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="X39" t="n">
-        <v>3.75</v>
+        <v>2.833</v>
       </c>
       <c r="Y39" t="n">
-        <v>12</v>
+        <v>11.167</v>
       </c>
       <c r="Z39" t="n">
-        <v>16.75</v>
+        <v>15.667</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.716</v>
+        <v>0.713</v>
       </c>
       <c r="AB39" t="n">
-        <v>3.25</v>
+        <v>3.667</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.25</v>
+        <v>8.833</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.394</v>
+        <v>0.415</v>
       </c>
       <c r="AE39" t="n">
-        <v>5</v>
+        <v>5.667</v>
       </c>
       <c r="AF39" t="n">
-        <v>13</v>
+        <v>13.667</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.385</v>
+        <v>0.415</v>
       </c>
       <c r="AH39" t="n">
         <v>3</v>
       </c>
       <c r="AI39" t="n">
-        <v>6</v>
+        <v>5.833</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.5</v>
+        <v>0.514</v>
       </c>
       <c r="AK39" t="n">
-        <v>7.75</v>
+        <v>7.333</v>
       </c>
       <c r="AL39" t="n">
-        <v>20.75</v>
+        <v>20.5</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.373</v>
+        <v>0.358</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
@@ -6365,34 +6365,34 @@
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>83.22</v>
+        <v>82.533</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.606</v>
+        <v>0.6</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.066</v>
+        <v>1.05</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.247</v>
+        <v>0.227</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.625</v>
+        <v>1.548</v>
       </c>
       <c r="AV39" t="n">
         <v>0.2</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.038</v>
+        <v>0.043</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.133</v>
+        <v>0.131</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -6405,40 +6405,40 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C40" t="n">
-        <v>102.5</v>
+        <v>98.667</v>
       </c>
       <c r="D40" t="n">
-        <v>29</v>
+        <v>26.167</v>
       </c>
       <c r="E40" t="n">
-        <v>44.75</v>
+        <v>41.833</v>
       </c>
       <c r="F40" t="n">
-        <v>8.25</v>
+        <v>8.667</v>
       </c>
       <c r="G40" t="n">
-        <v>22.25</v>
+        <v>22.167</v>
       </c>
       <c r="H40" t="n">
-        <v>19.75</v>
+        <v>20.333</v>
       </c>
       <c r="I40" t="n">
-        <v>24.5</v>
+        <v>24.833</v>
       </c>
       <c r="J40" t="n">
-        <v>17.75</v>
+        <v>16.667</v>
       </c>
       <c r="K40" t="n">
-        <v>28</v>
+        <v>26.5</v>
       </c>
       <c r="L40" t="n">
-        <v>10.25</v>
+        <v>10.167</v>
       </c>
       <c r="M40" t="n">
-        <v>5.25</v>
+        <v>5.833</v>
       </c>
       <c r="N40" t="n">
         <v>4.5</v>
@@ -6447,76 +6447,76 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>8.75</v>
+        <v>9.667</v>
       </c>
       <c r="Q40" t="n">
-        <v>7.75</v>
+        <v>8.667</v>
       </c>
       <c r="R40" t="n">
         <v>22</v>
       </c>
       <c r="S40" t="n">
-        <v>24</v>
+        <v>23.333</v>
       </c>
       <c r="T40" t="n">
-        <v>508</v>
+        <v>722</v>
       </c>
       <c r="U40" t="n">
         <v>9</v>
       </c>
       <c r="V40" t="n">
-        <v>10</v>
+        <v>11.333</v>
       </c>
       <c r="W40" t="n">
-        <v>7.75</v>
+        <v>5.667</v>
       </c>
       <c r="X40" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>19.5</v>
+        <v>16.667</v>
       </c>
       <c r="Z40" t="n">
-        <v>25</v>
+        <v>22.333</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.78</v>
+        <v>0.746</v>
       </c>
       <c r="AB40" t="n">
-        <v>6.25</v>
+        <v>5.333</v>
       </c>
       <c r="AC40" t="n">
-        <v>12.5</v>
+        <v>10.833</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.5</v>
+        <v>0.492</v>
       </c>
       <c r="AE40" t="n">
-        <v>3.25</v>
+        <v>4.167</v>
       </c>
       <c r="AF40" t="n">
-        <v>7.25</v>
+        <v>8.667</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.448</v>
+        <v>0.481</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AI40" t="n">
-        <v>4</v>
+        <v>3.833</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.438</v>
+        <v>0.522</v>
       </c>
       <c r="AK40" t="n">
-        <v>6.5</v>
+        <v>6.667</v>
       </c>
       <c r="AL40" t="n">
-        <v>18.25</v>
+        <v>18.333</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.356</v>
+        <v>0.364</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
@@ -6524,34 +6524,34 @@
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>86.53</v>
+        <v>84.593</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.618</v>
+        <v>0.612</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.659</v>
+        <v>0.658</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.185</v>
+        <v>1.166</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.101</v>
+        <v>0.114</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.295</v>
+        <v>0.318</v>
       </c>
       <c r="AU40" t="n">
-        <v>2.029</v>
+        <v>1.724</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.184</v>
+        <v>0.179</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>

--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_La Laguna Tenerife.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_La Laguna Tenerife.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,212 +417,212 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>POSSind</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>POSSest</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>OER</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>DER</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>eFG%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>TOV%</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ORB%</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>FTR</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>TOpts</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2CPts</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>FastBPts</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>TOunf</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Rim FGM</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Rim FGA</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Rim_vol</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Paint FGM</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Paint FGA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Paint_vol</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>MR FGM</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>MR FGA</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>MR_vol</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Cor3 FGM</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Cor3 FGA</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Cor3_vol</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ATB3 FGM</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ATB3 FGA</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ATB3_vol</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Rim %</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Paint %</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>MR %</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Cor3 %</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ATB3 %</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Rim PPS</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>MR PPS</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>3P PPS</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>TOptsPPO</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>2CPtsPPO</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>FastBPtsPPO</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Ass/TO</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Sh/TO</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Gen/TO</t>
         </is>
@@ -1161,259 +1149,259 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>2PM</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>2PA</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>3PM</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>3PA</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>FTM</t>
         </is>
       </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>FTA</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>AS</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>DRB</t>
         </is>
       </c>
-      <c r="L7" s="1" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>ORB</t>
         </is>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="N7" s="1" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>BLK</t>
         </is>
       </c>
-      <c r="O7" s="1" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>BLK A.</t>
         </is>
       </c>
-      <c r="P7" s="1" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="Q7" s="1" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>TOunf</t>
         </is>
       </c>
-      <c r="R7" s="1" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="S7" s="1" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>F+</t>
         </is>
       </c>
-      <c r="T7" s="1" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>EFI</t>
         </is>
       </c>
-      <c r="U7" s="1" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>TOpts</t>
         </is>
       </c>
-      <c r="V7" s="1" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>2CPts</t>
         </is>
       </c>
-      <c r="W7" s="1" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>FastBPts</t>
         </is>
       </c>
-      <c r="X7" s="1" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>FastB Opp</t>
         </is>
       </c>
-      <c r="Y7" s="1" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Rim FGM</t>
         </is>
       </c>
-      <c r="Z7" s="1" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Rim FGA</t>
         </is>
       </c>
-      <c r="AA7" s="1" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Rim %</t>
         </is>
       </c>
-      <c r="AB7" s="1" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Paint FGM</t>
         </is>
       </c>
-      <c r="AC7" s="1" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Paint FGA</t>
         </is>
       </c>
-      <c r="AD7" s="1" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Paint %</t>
         </is>
       </c>
-      <c r="AE7" s="1" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>MR FGM</t>
         </is>
       </c>
-      <c r="AF7" s="1" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>MR FGA</t>
         </is>
       </c>
-      <c r="AG7" s="1" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>MR %</t>
         </is>
       </c>
-      <c r="AH7" s="1" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>Cor3 FGM</t>
         </is>
       </c>
-      <c r="AI7" s="1" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>Cor3 FGA</t>
         </is>
       </c>
-      <c r="AJ7" s="1" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Cor3 %</t>
         </is>
       </c>
-      <c r="AK7" s="1" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>ATB3 FGM</t>
         </is>
       </c>
-      <c r="AL7" s="1" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>ATB3 FGA</t>
         </is>
       </c>
-      <c r="AM7" s="1" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>ATB3 %</t>
         </is>
       </c>
-      <c r="AN7" s="1" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="AO7" s="1" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>PLAYS</t>
         </is>
       </c>
-      <c r="AP7" s="1" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>eFG%</t>
         </is>
       </c>
-      <c r="AQ7" s="1" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>TS%</t>
         </is>
       </c>
-      <c r="AR7" s="1" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>PTS/PLAY</t>
         </is>
       </c>
-      <c r="AS7" s="1" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>TO%</t>
         </is>
       </c>
-      <c r="AT7" s="1" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>FTR</t>
         </is>
       </c>
-      <c r="AU7" s="1" t="inlineStr">
+      <c r="AU7" t="inlineStr">
         <is>
           <t>Ass/TO</t>
         </is>
       </c>
-      <c r="AV7" s="1" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>USG%</t>
         </is>
       </c>
-      <c r="AW7" s="1" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>OR%</t>
         </is>
       </c>
-      <c r="AX7" s="1" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>DR%</t>
         </is>
       </c>
-      <c r="AY7" s="1" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>pAST%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>#3 J. FERNÁNDEZ</t>
         </is>
@@ -1572,7 +1560,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>#4 W. VAN BECK</t>
         </is>
@@ -1731,7 +1719,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>#9 M. HUERTAS</t>
         </is>
@@ -1890,7 +1878,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>#10 E. FRIDRIKSSON</t>
         </is>
@@ -2049,7 +2037,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>#11 T. SCRUBB</t>
         </is>
@@ -2208,7 +2196,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>#15 J. SASTRE</t>
         </is>
@@ -2367,7 +2355,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>#16 D. BORDÓN</t>
         </is>
@@ -2526,7 +2514,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>#21 T. ABROMAITIS</t>
         </is>
@@ -2685,7 +2673,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>#25 K. YEBO</t>
         </is>
@@ -2844,7 +2832,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>#33 H. ALDERETE</t>
         </is>
@@ -3003,7 +2991,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>#35 F. GUERRA</t>
         </is>
@@ -3162,7 +3150,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>#42 A. DOORNEKAMP</t>
         </is>
@@ -3321,7 +3309,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>#88 P. MILLS</t>
         </is>
@@ -3480,7 +3468,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Equip</t>
         </is>
@@ -3639,7 +3627,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -3798,7 +3786,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Rival</t>
         </is>
@@ -3957,7 +3945,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>--- PER GAME STATS ---</t>
         </is>
@@ -4014,7 +4002,7 @@
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>#3 J. FERNÁNDEZ (Per Game)</t>
         </is>
@@ -4173,7 +4161,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>#4 W. VAN BECK (Per Game)</t>
         </is>
@@ -4332,7 +4320,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>#9 M. HUERTAS (Per Game)</t>
         </is>
@@ -4491,7 +4479,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>#10 E. FRIDRIKSSON (Per Game)</t>
         </is>
@@ -4650,7 +4638,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>#11 T. SCRUBB (Per Game)</t>
         </is>
@@ -4809,7 +4797,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>#15 J. SASTRE (Per Game)</t>
         </is>
@@ -4968,7 +4956,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>#16 D. BORDÓN (Per Game)</t>
         </is>
@@ -5127,7 +5115,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>#21 T. ABROMAITIS (Per Game)</t>
         </is>
@@ -5286,7 +5274,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>#25 K. YEBO (Per Game)</t>
         </is>
@@ -5445,7 +5433,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>#33 H. ALDERETE (Per Game)</t>
         </is>
@@ -5604,7 +5592,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>#35 F. GUERRA (Per Game)</t>
         </is>
@@ -5763,7 +5751,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>#42 A. DOORNEKAMP (Per Game)</t>
         </is>
@@ -5922,7 +5910,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>#88 P. MILLS (Per Game)</t>
         </is>
@@ -6081,7 +6069,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Equip (Per Game)</t>
         </is>
@@ -6240,7 +6228,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>TOTAL (Per Game)</t>
         </is>
@@ -6399,7 +6387,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Rival (Per Game)</t>
         </is>
